--- a/research/traditional_assets/database/data/italy/italy_trucking.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_trucking.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059368505834898</v>
+        <v>0.1057168021420894</v>
       </c>
       <c r="C2">
-        <v>39.45757950131013</v>
+        <v>39.19889849336985</v>
       </c>
       <c r="D2">
-        <v>36.92757950131013</v>
+        <v>37.06319849336985</v>
       </c>
       <c r="E2">
-        <v>-7.43</v>
+        <v>-7.035699999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="G2">
         <v>2.53</v>
@@ -1439,28 +1439,28 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01983329</v>
       </c>
       <c r="N2">
-        <v>0.6600000000000001</v>
+        <v>0.6401667100000001</v>
       </c>
       <c r="O2">
-        <v>0.1584</v>
+        <v>0.1536400104</v>
       </c>
       <c r="P2">
-        <v>0.5016</v>
+        <v>0.4865266996000001</v>
       </c>
       <c r="Q2">
-        <v>2.4816</v>
+        <v>2.4665266996</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059368505834898</v>
+        <v>0.1063985072142318</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.8341612613839667</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>33.27738363125837</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1057168021420894</v>
+        <v>0.1054967537006891</v>
       </c>
       <c r="C3">
-        <v>39.19889849336985</v>
+        <v>38.94121729684231</v>
       </c>
       <c r="D3">
-        <v>37.06319849336985</v>
+        <v>37.19981729684231</v>
       </c>
       <c r="E3">
-        <v>-7.035699999999999</v>
+        <v>-6.6414</v>
       </c>
       <c r="F3">
-        <v>0.3943</v>
+        <v>0.7886</v>
       </c>
       <c r="G3">
         <v>2.53</v>
@@ -1521,28 +1521,28 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M3">
-        <v>0.01983329</v>
+        <v>0.03966657999999999</v>
       </c>
       <c r="N3">
-        <v>0.6401667100000001</v>
+        <v>0.6203334200000001</v>
       </c>
       <c r="O3">
-        <v>0.1536400104</v>
+        <v>0.1488800208</v>
       </c>
       <c r="P3">
-        <v>0.4865266996000001</v>
+        <v>0.4714533992000001</v>
       </c>
       <c r="Q3">
-        <v>2.4665266996</v>
+        <v>2.4514533992</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1063985072142318</v>
+        <v>0.1068695854088664</v>
       </c>
       <c r="T3">
-        <v>0.8341612613839667</v>
+        <v>0.8406458300492922</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>33.27738363125837</v>
+        <v>16.63869181562918</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1054967537006891</v>
+        <v>0.1053109052592887</v>
       </c>
       <c r="C4">
-        <v>38.94121729684231</v>
+        <v>38.66308975355214</v>
       </c>
       <c r="D4">
-        <v>37.19981729684231</v>
+        <v>37.31598975355213</v>
       </c>
       <c r="E4">
-        <v>-6.6414</v>
+        <v>-6.2471</v>
       </c>
       <c r="F4">
-        <v>0.7886</v>
+        <v>1.1829</v>
       </c>
       <c r="G4">
         <v>2.53</v>
@@ -1603,45 +1603,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M4">
-        <v>0.03966657999999999</v>
+        <v>0.06127421999999999</v>
       </c>
       <c r="N4">
-        <v>0.6203334200000001</v>
+        <v>0.5987257800000001</v>
       </c>
       <c r="O4">
-        <v>0.1488800208</v>
+        <v>0.1436941872</v>
       </c>
       <c r="P4">
-        <v>0.4714533992000001</v>
+        <v>0.4550315928000001</v>
       </c>
       <c r="Q4">
-        <v>2.4514533992</v>
+        <v>2.4350315928</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1068695854088664</v>
+        <v>0.1073503765559678</v>
       </c>
       <c r="T4">
-        <v>0.8406458300492922</v>
+        <v>0.8472641011613256</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.63869181562918</v>
+        <v>10.77125094370847</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1053109052592887</v>
+        <v>0.1051539368178883</v>
       </c>
       <c r="C5">
-        <v>38.66308975355214</v>
+        <v>38.36747626138899</v>
       </c>
       <c r="D5">
-        <v>37.31598975355213</v>
+        <v>37.41467626138899</v>
       </c>
       <c r="E5">
-        <v>-6.2471</v>
+        <v>-5.8528</v>
       </c>
       <c r="F5">
-        <v>1.1829</v>
+        <v>1.5772</v>
       </c>
       <c r="G5">
         <v>2.53</v>
@@ -1685,45 +1685,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M5">
-        <v>0.06127421999999999</v>
+        <v>0.08438019999999999</v>
       </c>
       <c r="N5">
-        <v>0.5987257800000001</v>
+        <v>0.5756198000000001</v>
       </c>
       <c r="O5">
-        <v>0.1436941872</v>
+        <v>0.138148752</v>
       </c>
       <c r="P5">
-        <v>0.4550315928000001</v>
+        <v>0.4374710480000001</v>
       </c>
       <c r="Q5">
-        <v>2.4350315928</v>
+        <v>2.417471048</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1073503765559678</v>
+        <v>0.1078411841853004</v>
       </c>
       <c r="T5">
-        <v>0.8472641011613256</v>
+        <v>0.8540202529215262</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.77125094370847</v>
+        <v>7.82174017127241</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1051539368178883</v>
+        <v>0.104988608376488</v>
       </c>
       <c r="C6">
-        <v>38.36747626138899</v>
+        <v>38.07768471802391</v>
       </c>
       <c r="D6">
-        <v>37.41467626138899</v>
+        <v>37.51918471802391</v>
       </c>
       <c r="E6">
-        <v>-5.8528</v>
+        <v>-5.4585</v>
       </c>
       <c r="F6">
-        <v>1.5772</v>
+        <v>1.9715</v>
       </c>
       <c r="G6">
         <v>2.53</v>
@@ -1767,45 +1767,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M6">
-        <v>0.08438019999999999</v>
+        <v>0.10705245</v>
       </c>
       <c r="N6">
-        <v>0.5756198000000001</v>
+        <v>0.5529475500000002</v>
       </c>
       <c r="O6">
-        <v>0.138148752</v>
+        <v>0.132707412</v>
       </c>
       <c r="P6">
-        <v>0.4374710480000001</v>
+        <v>0.4202401380000002</v>
       </c>
       <c r="Q6">
-        <v>2.417471048</v>
+        <v>2.400240138</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1078411841853004</v>
+        <v>0.1083423246068294</v>
       </c>
       <c r="T6">
-        <v>0.8540202529215262</v>
+        <v>0.8609186394556256</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.82174017127241</v>
+        <v>6.165202197614348</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.104988608376488</v>
+        <v>0.1048445599350876</v>
       </c>
       <c r="C7">
-        <v>38.07768471802391</v>
+        <v>37.77491863896745</v>
       </c>
       <c r="D7">
-        <v>37.51918471802391</v>
+        <v>37.61071863896745</v>
       </c>
       <c r="E7">
-        <v>-5.4585</v>
+        <v>-5.0642</v>
       </c>
       <c r="F7">
-        <v>1.9715</v>
+        <v>2.3658</v>
       </c>
       <c r="G7">
         <v>2.53</v>
@@ -1849,45 +1849,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M7">
-        <v>0.10705245</v>
+        <v>0.13082874</v>
       </c>
       <c r="N7">
-        <v>0.5529475500000002</v>
+        <v>0.5291712600000001</v>
       </c>
       <c r="O7">
-        <v>0.132707412</v>
+        <v>0.1270011024</v>
       </c>
       <c r="P7">
-        <v>0.4202401380000002</v>
+        <v>0.4021701576000001</v>
       </c>
       <c r="Q7">
-        <v>2.400240138</v>
+        <v>2.3821701576</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1083423246068294</v>
+        <v>0.1088541275905187</v>
       </c>
       <c r="T7">
-        <v>0.8609186394556256</v>
+        <v>0.8679638001713018</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.165202197614348</v>
+        <v>5.044763100217889</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1048445599350876</v>
+        <v>0.1047955114936872</v>
       </c>
       <c r="C8">
-        <v>37.77491863896745</v>
+        <v>37.41188791831569</v>
       </c>
       <c r="D8">
-        <v>37.61071863896745</v>
+        <v>37.64198791831569</v>
       </c>
       <c r="E8">
-        <v>-5.0642</v>
+        <v>-4.6699</v>
       </c>
       <c r="F8">
-        <v>2.3658</v>
+        <v>2.7601</v>
       </c>
       <c r="G8">
         <v>2.53</v>
@@ -1931,45 +1931,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M8">
-        <v>0.13082874</v>
+        <v>0.15953378</v>
       </c>
       <c r="N8">
-        <v>0.5291712600000001</v>
+        <v>0.5004662200000002</v>
       </c>
       <c r="O8">
-        <v>0.1270011024</v>
+        <v>0.1201118928</v>
       </c>
       <c r="P8">
-        <v>0.4021701576000001</v>
+        <v>0.3803543272000002</v>
       </c>
       <c r="Q8">
-        <v>2.3821701576</v>
+        <v>2.3603543272</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1088541275905187</v>
+        <v>0.1093769370899862</v>
       </c>
       <c r="T8">
-        <v>0.8679638001713018</v>
+        <v>0.8751604697195731</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>5.044763100217889</v>
+        <v>4.137054860732318</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1047955114936872</v>
+        <v>0.1050155030522868</v>
       </c>
       <c r="C9">
-        <v>37.4118879183157</v>
+        <v>36.87774414153269</v>
       </c>
       <c r="D9">
-        <v>37.6419879183157</v>
+        <v>37.50214414153269</v>
       </c>
       <c r="E9">
-        <v>-4.669899999999999</v>
+        <v>-4.2756</v>
       </c>
       <c r="F9">
-        <v>2.7601</v>
+        <v>3.1544</v>
       </c>
       <c r="G9">
         <v>2.53</v>
@@ -2013,45 +2013,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M9">
-        <v>0.15953378</v>
+        <v>0.20219704</v>
       </c>
       <c r="N9">
-        <v>0.5004662200000001</v>
+        <v>0.4578029600000001</v>
       </c>
       <c r="O9">
-        <v>0.1201118928</v>
+        <v>0.1098727104</v>
       </c>
       <c r="P9">
-        <v>0.3803543272000001</v>
+        <v>0.3479302496000001</v>
       </c>
       <c r="Q9">
-        <v>2.3603543272</v>
+        <v>2.3279302496</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1093769370899862</v>
+        <v>0.1099111120133552</v>
       </c>
       <c r="T9">
-        <v>0.8751604697195731</v>
+        <v>0.8825135886058503</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.043928</v>
+        <v>0.048716</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.137054860732317</v>
+        <v>3.264142739181544</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1050155030522868</v>
+        <v>0.1054338546108865</v>
       </c>
       <c r="C10">
-        <v>36.87774414153269</v>
+        <v>36.22035397983158</v>
       </c>
       <c r="D10">
-        <v>37.50214414153269</v>
+        <v>37.23905397983157</v>
       </c>
       <c r="E10">
-        <v>-4.2756</v>
+        <v>-3.8813</v>
       </c>
       <c r="F10">
-        <v>3.1544</v>
+        <v>3.5487</v>
       </c>
       <c r="G10">
         <v>2.53</v>
@@ -2095,45 +2095,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M10">
-        <v>0.20219704</v>
+        <v>0.25515153</v>
       </c>
       <c r="N10">
-        <v>0.4578029600000001</v>
+        <v>0.4048484700000001</v>
       </c>
       <c r="O10">
-        <v>0.1098727104</v>
+        <v>0.09716363280000002</v>
       </c>
       <c r="P10">
-        <v>0.3479302496000001</v>
+        <v>0.3076848372000001</v>
       </c>
       <c r="Q10">
-        <v>2.3279302496</v>
+        <v>2.2876848372</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1099111120133552</v>
+        <v>0.1104570270449302</v>
       </c>
       <c r="T10">
-        <v>0.8825135886058503</v>
+        <v>0.8900283145006171</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.264142739181544</v>
+        <v>2.586698186759845</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1054338546108865</v>
+        <v>0.1056743661694861</v>
       </c>
       <c r="C11">
-        <v>36.22035397983158</v>
+        <v>35.67646704494675</v>
       </c>
       <c r="D11">
-        <v>37.23905397983157</v>
+        <v>37.08946704494675</v>
       </c>
       <c r="E11">
-        <v>-3.8813</v>
+        <v>-3.487</v>
       </c>
       <c r="F11">
-        <v>3.5487</v>
+        <v>3.943</v>
       </c>
       <c r="G11">
         <v>2.53</v>
@@ -2177,45 +2177,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M11">
-        <v>0.25515153</v>
+        <v>0.2988794</v>
       </c>
       <c r="N11">
-        <v>0.4048484700000001</v>
+        <v>0.3611206000000001</v>
       </c>
       <c r="O11">
-        <v>0.09716363280000002</v>
+        <v>0.08666894400000003</v>
       </c>
       <c r="P11">
-        <v>0.3076848372000001</v>
+        <v>0.2744516560000001</v>
       </c>
       <c r="Q11">
-        <v>2.2876848372</v>
+        <v>2.254451656</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1104570270449302</v>
+        <v>0.1110150735216512</v>
       </c>
       <c r="T11">
-        <v>0.8900283145006171</v>
+        <v>0.8977100343041567</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.586698186759845</v>
+        <v>2.208248544396168</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1056743661694861</v>
+        <v>0.1056481177280857</v>
       </c>
       <c r="C12">
-        <v>35.67646704494675</v>
+        <v>35.29843390076875</v>
       </c>
       <c r="D12">
-        <v>37.08946704494675</v>
+        <v>37.10573390076875</v>
       </c>
       <c r="E12">
-        <v>-3.487</v>
+        <v>-3.0927</v>
       </c>
       <c r="F12">
-        <v>3.943</v>
+        <v>4.3373</v>
       </c>
       <c r="G12">
         <v>2.53</v>
@@ -2259,28 +2259,28 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M12">
-        <v>0.2988794</v>
+        <v>0.32876734</v>
       </c>
       <c r="N12">
-        <v>0.3611206000000001</v>
+        <v>0.3312326600000001</v>
       </c>
       <c r="O12">
-        <v>0.08666894400000003</v>
+        <v>0.07949583840000003</v>
       </c>
       <c r="P12">
-        <v>0.2744516560000001</v>
+        <v>0.2517368216000001</v>
       </c>
       <c r="Q12">
-        <v>2.254451656</v>
+        <v>2.2317368216</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1110150735216512</v>
+        <v>0.1115856603686356</v>
       </c>
       <c r="T12">
-        <v>0.8977100343041567</v>
+        <v>0.9055643770246297</v>
       </c>
       <c r="U12">
         <v>0.07580000000000001</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>2.208248544396168</v>
+        <v>2.007498676723789</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1056481177280857</v>
+        <v>0.1069169092866853</v>
       </c>
       <c r="C13">
-        <v>35.29843390076875</v>
+        <v>34.13381611967645</v>
       </c>
       <c r="D13">
-        <v>37.10573390076875</v>
+        <v>36.33541611967645</v>
       </c>
       <c r="E13">
-        <v>-3.0927</v>
+        <v>-2.6984</v>
       </c>
       <c r="F13">
-        <v>4.3373</v>
+        <v>4.731599999999999</v>
       </c>
       <c r="G13">
         <v>2.53</v>
@@ -2341,45 +2341,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M13">
-        <v>0.32876734</v>
+        <v>0.4258439999999999</v>
       </c>
       <c r="N13">
-        <v>0.3312326600000001</v>
+        <v>0.2341560000000002</v>
       </c>
       <c r="O13">
-        <v>0.07949583840000003</v>
+        <v>0.05619744000000004</v>
       </c>
       <c r="P13">
-        <v>0.2517368216000001</v>
+        <v>0.1779585600000002</v>
       </c>
       <c r="Q13">
-        <v>2.2317368216</v>
+        <v>2.15795856</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1115856603686356</v>
+        <v>0.1121692150985061</v>
       </c>
       <c r="T13">
-        <v>0.9055643770246297</v>
+        <v>0.913597227534204</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.007498676723789</v>
+        <v>1.549863330233607</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1069169092866853</v>
+        <v>0.1134039337992143</v>
       </c>
       <c r="C14">
-        <v>34.13381611967645</v>
+        <v>30.25290340655617</v>
       </c>
       <c r="D14">
-        <v>36.33541611967645</v>
+        <v>32.84880340655617</v>
       </c>
       <c r="E14">
-        <v>-2.6984</v>
+        <v>-2.304099999999999</v>
       </c>
       <c r="F14">
-        <v>4.731599999999999</v>
+        <v>5.125900000000001</v>
       </c>
       <c r="G14">
         <v>2.53</v>
@@ -2423,45 +2423,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M14">
-        <v>0.4258439999999999</v>
+        <v>0.7524821200000001</v>
       </c>
       <c r="N14">
-        <v>0.2341560000000002</v>
+        <v>-0.09248212</v>
       </c>
       <c r="O14">
-        <v>0.05619744000000004</v>
+        <v>-0.0221957088</v>
       </c>
       <c r="P14">
-        <v>0.1779585600000002</v>
+        <v>-0.07028641120000001</v>
       </c>
       <c r="Q14">
-        <v>2.15795856</v>
+        <v>1.9097135888</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1121692150985061</v>
+        <v>0.1130312408634251</v>
       </c>
       <c r="T14">
-        <v>0.913597227534204</v>
+        <v>0.9254633366591078</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.24</v>
+        <v>0.2105033405976477</v>
       </c>
       <c r="W14">
-        <v>0.0684</v>
+        <v>0.1158981096002653</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.549863330233607</v>
+        <v>0.8770972524901988</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1134039337992143</v>
+        <v>0.1144139337992143</v>
       </c>
       <c r="C15">
-        <v>30.25290340655617</v>
+        <v>29.37506763468643</v>
       </c>
       <c r="D15">
-        <v>32.84880340655617</v>
+        <v>32.36526763468643</v>
       </c>
       <c r="E15">
-        <v>-2.304099999999999</v>
+        <v>-1.909799999999999</v>
       </c>
       <c r="F15">
-        <v>5.125900000000001</v>
+        <v>5.520200000000001</v>
       </c>
       <c r="G15">
         <v>2.53</v>
@@ -2505,37 +2505,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M15">
-        <v>0.7524821200000001</v>
+        <v>0.8103653600000003</v>
       </c>
       <c r="N15">
-        <v>-0.09248212</v>
+        <v>-0.1503653600000001</v>
       </c>
       <c r="O15">
-        <v>-0.0221957088</v>
+        <v>-0.03608768640000003</v>
       </c>
       <c r="P15">
-        <v>-0.07028641120000001</v>
+        <v>-0.1142776736000001</v>
       </c>
       <c r="Q15">
-        <v>1.9097135888</v>
+        <v>1.8657223264</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1130312408634251</v>
+        <v>0.1138129994781161</v>
       </c>
       <c r="T15">
-        <v>0.9254633366591078</v>
+        <v>0.9362245382481673</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.2105033405976477</v>
+        <v>0.1954673876978157</v>
       </c>
       <c r="W15">
-        <v>0.1158981096002653</v>
+        <v>0.1181053874859607</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8770972524901988</v>
+        <v>0.8144474487408987</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1144139337992143</v>
+        <v>0.1239664947341981</v>
       </c>
       <c r="C16">
-        <v>29.37506763468643</v>
+        <v>25.02547717029087</v>
       </c>
       <c r="D16">
-        <v>32.36526763468643</v>
+        <v>28.40997717029087</v>
       </c>
       <c r="E16">
-        <v>-1.909799999999999</v>
+        <v>-1.515499999999999</v>
       </c>
       <c r="F16">
-        <v>5.520200000000001</v>
+        <v>5.914500000000001</v>
       </c>
       <c r="G16">
         <v>2.53</v>
@@ -2587,45 +2587,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M16">
-        <v>0.8103653600000003</v>
+        <v>1.1876316</v>
       </c>
       <c r="N16">
-        <v>-0.1503653600000001</v>
+        <v>-0.5276316000000001</v>
       </c>
       <c r="O16">
-        <v>-0.03608768640000003</v>
+        <v>-0.126631584</v>
       </c>
       <c r="P16">
-        <v>-0.1142776736000001</v>
+        <v>-0.4010000160000001</v>
       </c>
       <c r="Q16">
-        <v>1.8657223264</v>
+        <v>1.578999984</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1138129994781161</v>
+        <v>0.1151338123366631</v>
       </c>
       <c r="T16">
-        <v>0.9362245382481673</v>
+        <v>0.9544060244066077</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.1954673876978157</v>
+        <v>0.1333746929603423</v>
       </c>
       <c r="W16">
-        <v>0.1181053874859607</v>
+        <v>0.1740183616535633</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8144474487408987</v>
+        <v>0.5557278873347593</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1239664947341981</v>
+        <v>0.1255164947341981</v>
       </c>
       <c r="C17">
-        <v>25.02547717029087</v>
+        <v>24.07877625551433</v>
       </c>
       <c r="D17">
-        <v>28.40997717029087</v>
+        <v>27.85757625551433</v>
       </c>
       <c r="E17">
-        <v>-1.5155</v>
+        <v>-1.1212</v>
       </c>
       <c r="F17">
-        <v>5.914499999999999</v>
+        <v>6.3088</v>
       </c>
       <c r="G17">
         <v>2.53</v>
@@ -2669,37 +2669,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M17">
-        <v>1.1876316</v>
+        <v>1.26680704</v>
       </c>
       <c r="N17">
-        <v>-0.5276315999999999</v>
+        <v>-0.6068070399999999</v>
       </c>
       <c r="O17">
-        <v>-0.126631584</v>
+        <v>-0.1456336895999999</v>
       </c>
       <c r="P17">
-        <v>-0.4010000159999999</v>
+        <v>-0.4611733503999999</v>
       </c>
       <c r="Q17">
-        <v>1.578999984</v>
+        <v>1.5188266496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1151338123366631</v>
+        <v>0.1159592148644805</v>
       </c>
       <c r="T17">
-        <v>0.9544060244066077</v>
+        <v>0.9657680008876387</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1333746929603423</v>
+        <v>0.1250387746503209</v>
       </c>
       <c r="W17">
-        <v>0.1740183616535633</v>
+        <v>0.1756922140502156</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5557278873347595</v>
+        <v>0.5209948943763369</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1255164947341981</v>
+        <v>0.1331950734170073</v>
       </c>
       <c r="C18">
-        <v>24.07877625551433</v>
+        <v>21.2368944545395</v>
       </c>
       <c r="D18">
-        <v>27.85757625551433</v>
+        <v>25.4099944545395</v>
       </c>
       <c r="E18">
-        <v>-1.1212</v>
+        <v>-0.7268999999999997</v>
       </c>
       <c r="F18">
-        <v>6.3088</v>
+        <v>6.7031</v>
       </c>
       <c r="G18">
         <v>2.53</v>
@@ -2751,45 +2751,45 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M18">
-        <v>1.26680704</v>
+        <v>1.58059098</v>
       </c>
       <c r="N18">
-        <v>-0.6068070399999999</v>
+        <v>-0.9205909799999998</v>
       </c>
       <c r="O18">
-        <v>-0.1456336895999999</v>
+        <v>-0.2209418352</v>
       </c>
       <c r="P18">
-        <v>-0.4611733503999999</v>
+        <v>-0.6996491447999998</v>
       </c>
       <c r="Q18">
-        <v>1.5188266496</v>
+        <v>1.2803508552</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1159592148644805</v>
+        <v>0.1170196616493649</v>
       </c>
       <c r="T18">
-        <v>0.9657680008876387</v>
+        <v>0.9803654500390262</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.1250387746503209</v>
+        <v>0.1002156800869508</v>
       </c>
       <c r="W18">
-        <v>0.1756922140502156</v>
+        <v>0.212169142635497</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5209948943763369</v>
+        <v>0.4175653336956283</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1331950734170073</v>
+        <v>0.1350950734170073</v>
       </c>
       <c r="C19">
-        <v>21.2368944545395</v>
+        <v>20.30192644659508</v>
       </c>
       <c r="D19">
-        <v>25.4099944545395</v>
+        <v>24.86932644659507</v>
       </c>
       <c r="E19">
-        <v>-0.7268999999999997</v>
+        <v>-0.3325999999999993</v>
       </c>
       <c r="F19">
-        <v>6.7031</v>
+        <v>7.0974</v>
       </c>
       <c r="G19">
         <v>2.53</v>
@@ -2833,37 +2833,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M19">
-        <v>1.58059098</v>
+        <v>1.67356692</v>
       </c>
       <c r="N19">
-        <v>-0.9205909799999998</v>
+        <v>-1.01356692</v>
       </c>
       <c r="O19">
-        <v>-0.2209418352</v>
+        <v>-0.2432560608</v>
       </c>
       <c r="P19">
-        <v>-0.6996491447999998</v>
+        <v>-0.7703108592</v>
       </c>
       <c r="Q19">
-        <v>1.2803508552</v>
+        <v>1.2096891408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1170196616493649</v>
+        <v>0.1178881941085035</v>
       </c>
       <c r="T19">
-        <v>0.9803654500390262</v>
+        <v>0.9923211262590143</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.1002156800869508</v>
+        <v>0.0946481423043424</v>
       </c>
       <c r="W19">
-        <v>0.212169142635497</v>
+        <v>0.2134819680446361</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.4175653336956283</v>
+        <v>0.3943672596014267</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1350950734170073</v>
+        <v>0.1369950734170073</v>
       </c>
       <c r="C20">
-        <v>20.30192644659508</v>
+        <v>19.38948748932417</v>
       </c>
       <c r="D20">
-        <v>24.86932644659507</v>
+        <v>24.35118748932418</v>
       </c>
       <c r="E20">
-        <v>-0.3326000000000002</v>
+        <v>0.06170000000000009</v>
       </c>
       <c r="F20">
-        <v>7.097399999999999</v>
+        <v>7.4917</v>
       </c>
       <c r="G20">
         <v>2.53</v>
@@ -2915,37 +2915,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M20">
-        <v>1.67356692</v>
+        <v>1.76654286</v>
       </c>
       <c r="N20">
-        <v>-1.01356692</v>
+        <v>-1.10654286</v>
       </c>
       <c r="O20">
-        <v>-0.2432560607999999</v>
+        <v>-0.2655702864</v>
       </c>
       <c r="P20">
-        <v>-0.7703108591999998</v>
+        <v>-0.8409725735999998</v>
       </c>
       <c r="Q20">
-        <v>1.2096891408</v>
+        <v>1.1390274264</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1178881941085035</v>
+        <v>0.1187781718135467</v>
       </c>
       <c r="T20">
-        <v>0.9923211262590143</v>
+        <v>1.004572004360977</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.09464814230434242</v>
+        <v>0.08966666113042965</v>
       </c>
       <c r="W20">
-        <v>0.2134819680446361</v>
+        <v>0.2146566013054447</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3943672596014267</v>
+        <v>0.3736110880434569</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1369950734170073</v>
+        <v>0.1388950734170074</v>
       </c>
       <c r="C21">
-        <v>19.38948748932417</v>
+        <v>18.49819818009975</v>
       </c>
       <c r="D21">
-        <v>24.35118748932418</v>
+        <v>23.85419818009975</v>
       </c>
       <c r="E21">
-        <v>0.06170000000000009</v>
+        <v>0.4560000000000004</v>
       </c>
       <c r="F21">
-        <v>7.4917</v>
+        <v>7.886</v>
       </c>
       <c r="G21">
         <v>2.53</v>
@@ -2997,37 +2997,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M21">
-        <v>1.76654286</v>
+        <v>1.8595188</v>
       </c>
       <c r="N21">
-        <v>-1.10654286</v>
+        <v>-1.1995188</v>
       </c>
       <c r="O21">
-        <v>-0.2655702864</v>
+        <v>-0.287884512</v>
       </c>
       <c r="P21">
-        <v>-0.8409725735999998</v>
+        <v>-0.9116342879999999</v>
       </c>
       <c r="Q21">
-        <v>1.1390274264</v>
+        <v>1.068365712</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1187781718135467</v>
+        <v>0.1196903989612161</v>
       </c>
       <c r="T21">
-        <v>1.004572004360977</v>
+        <v>1.01712915441549</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.08966666113042965</v>
+        <v>0.08518332807390816</v>
       </c>
       <c r="W21">
-        <v>0.2146566013054447</v>
+        <v>0.2157137712401725</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3736110880434569</v>
+        <v>0.354930533641284</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1388950734170074</v>
+        <v>0.1407950734170073</v>
       </c>
       <c r="C22">
-        <v>18.49819818009975</v>
+        <v>17.62678947422791</v>
       </c>
       <c r="D22">
-        <v>23.85419818009975</v>
+        <v>23.3770894742279</v>
       </c>
       <c r="E22">
-        <v>0.4560000000000004</v>
+        <v>0.8503000000000007</v>
       </c>
       <c r="F22">
-        <v>7.886</v>
+        <v>8.2803</v>
       </c>
       <c r="G22">
         <v>2.53</v>
@@ -3079,37 +3079,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M22">
-        <v>1.8595188</v>
+        <v>1.95249474</v>
       </c>
       <c r="N22">
-        <v>-1.1995188</v>
+        <v>-1.29249474</v>
       </c>
       <c r="O22">
-        <v>-0.287884512</v>
+        <v>-0.3101987376</v>
       </c>
       <c r="P22">
-        <v>-0.9116342879999999</v>
+        <v>-0.9822960024</v>
       </c>
       <c r="Q22">
-        <v>1.068365712</v>
+        <v>0.9977039975999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1196903989612161</v>
+        <v>0.1206257204670542</v>
       </c>
       <c r="T22">
-        <v>1.01712915441549</v>
+        <v>1.030004207003028</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.08518332807390816</v>
+        <v>0.08112697911800779</v>
       </c>
       <c r="W22">
-        <v>0.2157137712401725</v>
+        <v>0.2166702583239738</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.354930533641284</v>
+        <v>0.3380290796583657</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1407950734170073</v>
+        <v>0.1426950734170073</v>
       </c>
       <c r="C23">
-        <v>17.62678947422791</v>
+        <v>16.77409186499263</v>
       </c>
       <c r="D23">
-        <v>23.3770894742279</v>
+        <v>22.91869186499263</v>
       </c>
       <c r="E23">
-        <v>0.8503000000000007</v>
+        <v>1.2446</v>
       </c>
       <c r="F23">
-        <v>8.2803</v>
+        <v>8.6746</v>
       </c>
       <c r="G23">
         <v>2.53</v>
@@ -3161,37 +3161,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M23">
-        <v>1.95249474</v>
+        <v>2.04547068</v>
       </c>
       <c r="N23">
-        <v>-1.29249474</v>
+        <v>-1.38547068</v>
       </c>
       <c r="O23">
-        <v>-0.3101987376</v>
+        <v>-0.3325129632</v>
       </c>
       <c r="P23">
-        <v>-0.9822960024</v>
+        <v>-1.0529577168</v>
       </c>
       <c r="Q23">
-        <v>0.9977039975999999</v>
+        <v>0.9270422832</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1206257204670542</v>
+        <v>0.1215850245756062</v>
       </c>
       <c r="T23">
-        <v>1.030004207003028</v>
+        <v>1.043209389144092</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.08112697911800779</v>
+        <v>0.07743938915809832</v>
       </c>
       <c r="W23">
-        <v>0.2166702583239738</v>
+        <v>0.2175397920365204</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3380290796583657</v>
+        <v>0.3226641214920764</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1426950734170073</v>
+        <v>0.1445950734170073</v>
       </c>
       <c r="C24">
-        <v>16.77409186499263</v>
+        <v>15.93902581221909</v>
       </c>
       <c r="D24">
-        <v>22.91869186499263</v>
+        <v>22.47792581221909</v>
       </c>
       <c r="E24">
-        <v>1.2446</v>
+        <v>1.638900000000001</v>
       </c>
       <c r="F24">
-        <v>8.6746</v>
+        <v>9.068900000000001</v>
       </c>
       <c r="G24">
         <v>2.53</v>
@@ -3243,37 +3243,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M24">
-        <v>2.04547068</v>
+        <v>2.13844662</v>
       </c>
       <c r="N24">
-        <v>-1.38547068</v>
+        <v>-1.47844662</v>
       </c>
       <c r="O24">
-        <v>-0.3325129632</v>
+        <v>-0.3548271888</v>
       </c>
       <c r="P24">
-        <v>-1.0529577168</v>
+        <v>-1.1236194312</v>
       </c>
       <c r="Q24">
-        <v>0.9270422832</v>
+        <v>0.8563805687999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1215850245756062</v>
+        <v>0.1225692456739907</v>
       </c>
       <c r="T24">
-        <v>1.043209389144092</v>
+        <v>1.05675756302908</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.07743938915809832</v>
+        <v>0.07407245919470275</v>
       </c>
       <c r="W24">
-        <v>0.2175397920365204</v>
+        <v>0.2183337141218891</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3226641214920764</v>
+        <v>0.3086352466445947</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1445950734170073</v>
+        <v>0.1464950734170073</v>
       </c>
       <c r="C25">
-        <v>15.93902581221909</v>
+        <v>15.12059325444886</v>
       </c>
       <c r="D25">
-        <v>22.47792581221909</v>
+        <v>22.05379325444886</v>
       </c>
       <c r="E25">
-        <v>1.638900000000001</v>
+        <v>2.033200000000001</v>
       </c>
       <c r="F25">
-        <v>9.068900000000001</v>
+        <v>9.463200000000001</v>
       </c>
       <c r="G25">
         <v>2.53</v>
@@ -3325,37 +3325,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M25">
-        <v>2.13844662</v>
+        <v>2.23142256</v>
       </c>
       <c r="N25">
-        <v>-1.47844662</v>
+        <v>-1.57142256</v>
       </c>
       <c r="O25">
-        <v>-0.3548271888</v>
+        <v>-0.3771414144</v>
       </c>
       <c r="P25">
-        <v>-1.1236194312</v>
+        <v>-1.1942811456</v>
       </c>
       <c r="Q25">
-        <v>0.8563805687999999</v>
+        <v>0.7857188543999998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1225692456739907</v>
+        <v>0.1235793673275958</v>
       </c>
       <c r="T25">
-        <v>1.05675756302908</v>
+        <v>1.070662267805779</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.07407245919470275</v>
+        <v>0.0709861067282568</v>
       </c>
       <c r="W25">
-        <v>0.2183337141218891</v>
+        <v>0.2190614760334771</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3086352466445947</v>
+        <v>0.29577544470107</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1464950734170073</v>
+        <v>0.1483950734170073</v>
       </c>
       <c r="C26">
-        <v>15.12059325444887</v>
+        <v>14.31787006425202</v>
       </c>
       <c r="D26">
-        <v>22.05379325444887</v>
+        <v>21.64537006425202</v>
       </c>
       <c r="E26">
-        <v>2.033199999999999</v>
+        <v>2.4275</v>
       </c>
       <c r="F26">
-        <v>9.463199999999999</v>
+        <v>9.8575</v>
       </c>
       <c r="G26">
         <v>2.53</v>
@@ -3407,37 +3407,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M26">
-        <v>2.23142256</v>
+        <v>2.3243985</v>
       </c>
       <c r="N26">
-        <v>-1.57142256</v>
+        <v>-1.6643985</v>
       </c>
       <c r="O26">
-        <v>-0.3771414143999999</v>
+        <v>-0.3994556399999999</v>
       </c>
       <c r="P26">
-        <v>-1.1942811456</v>
+        <v>-1.26494286</v>
       </c>
       <c r="Q26">
-        <v>0.7857188544000002</v>
+        <v>0.7150571400000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1235793673275958</v>
+        <v>0.1246164255586305</v>
       </c>
       <c r="T26">
-        <v>1.070662267805779</v>
+        <v>1.084937764709856</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.07098610672825681</v>
+        <v>0.06814666245912654</v>
       </c>
       <c r="W26">
-        <v>0.2190614760334771</v>
+        <v>0.219731016992138</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2957754447010701</v>
+        <v>0.2839444269130272</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1483950734170073</v>
+        <v>0.1502950734170073</v>
       </c>
       <c r="C27">
-        <v>14.31787006425202</v>
+        <v>13.52999932663498</v>
       </c>
       <c r="D27">
-        <v>21.64537006425202</v>
+        <v>21.25179932663498</v>
       </c>
       <c r="E27">
-        <v>2.4275</v>
+        <v>2.821800000000001</v>
       </c>
       <c r="F27">
-        <v>9.8575</v>
+        <v>10.2518</v>
       </c>
       <c r="G27">
         <v>2.53</v>
@@ -3489,37 +3489,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M27">
-        <v>2.3243985</v>
+        <v>2.417374440000001</v>
       </c>
       <c r="N27">
-        <v>-1.6643985</v>
+        <v>-1.75737444</v>
       </c>
       <c r="O27">
-        <v>-0.3994556399999999</v>
+        <v>-0.4217698656000001</v>
       </c>
       <c r="P27">
-        <v>-1.26494286</v>
+        <v>-1.3356045744</v>
       </c>
       <c r="Q27">
-        <v>0.7150571400000001</v>
+        <v>0.6443954255999995</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1246164255586305</v>
+        <v>0.1256815123905038</v>
       </c>
       <c r="T27">
-        <v>1.084937764709856</v>
+        <v>1.099599085854583</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.06814666245912654</v>
+        <v>0.06552563697992934</v>
       </c>
       <c r="W27">
-        <v>0.219731016992138</v>
+        <v>0.2203490548001327</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2839444269130272</v>
+        <v>0.2730234874163723</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1502950734170073</v>
+        <v>0.1521950734170073</v>
       </c>
       <c r="C28">
-        <v>13.52999932663498</v>
+        <v>12.75618533765218</v>
       </c>
       <c r="D28">
-        <v>21.25179932663498</v>
+        <v>20.87228533765218</v>
       </c>
       <c r="E28">
-        <v>2.821800000000001</v>
+        <v>3.216100000000001</v>
       </c>
       <c r="F28">
-        <v>10.2518</v>
+        <v>10.6461</v>
       </c>
       <c r="G28">
         <v>2.53</v>
@@ -3571,37 +3571,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M28">
-        <v>2.417374440000001</v>
+        <v>2.51035038</v>
       </c>
       <c r="N28">
-        <v>-1.75737444</v>
+        <v>-1.85035038</v>
       </c>
       <c r="O28">
-        <v>-0.4217698656000001</v>
+        <v>-0.4440840912</v>
       </c>
       <c r="P28">
-        <v>-1.3356045744</v>
+        <v>-1.4062662888</v>
       </c>
       <c r="Q28">
-        <v>0.6443954255999995</v>
+        <v>0.5737337111999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1256815123905038</v>
+        <v>0.1267757796835245</v>
       </c>
       <c r="T28">
-        <v>1.099599085854583</v>
+        <v>1.114662087030674</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06552563697992934</v>
+        <v>0.06309876153622827</v>
       </c>
       <c r="W28">
-        <v>0.2203490548001327</v>
+        <v>0.2209213120297574</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2730234874163723</v>
+        <v>0.2629115064009512</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1521950734170073</v>
+        <v>0.1540950734170073</v>
       </c>
       <c r="C29">
-        <v>12.75618533765218</v>
+        <v>11.99568823477167</v>
       </c>
       <c r="D29">
-        <v>20.87228533765218</v>
+        <v>20.50608823477167</v>
       </c>
       <c r="E29">
-        <v>3.216100000000001</v>
+        <v>3.610400000000002</v>
       </c>
       <c r="F29">
-        <v>10.6461</v>
+        <v>11.0404</v>
       </c>
       <c r="G29">
         <v>2.53</v>
@@ -3653,37 +3653,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M29">
-        <v>2.51035038</v>
+        <v>2.60332632</v>
       </c>
       <c r="N29">
-        <v>-1.85035038</v>
+        <v>-1.94332632</v>
       </c>
       <c r="O29">
-        <v>-0.4440840912</v>
+        <v>-0.4663983168</v>
       </c>
       <c r="P29">
-        <v>-1.4062662888</v>
+        <v>-1.4769280032</v>
       </c>
       <c r="Q29">
-        <v>0.5737337111999998</v>
+        <v>0.5030719967999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1267757796835245</v>
+        <v>0.1279004432902401</v>
       </c>
       <c r="T29">
-        <v>1.114662087030674</v>
+        <v>1.1301435049061</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.06309876153622827</v>
+        <v>0.06084523433850583</v>
       </c>
       <c r="W29">
-        <v>0.2209213120297574</v>
+        <v>0.2214526937429803</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2629115064009512</v>
+        <v>0.2535218097437743</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1540950734170073</v>
+        <v>0.1559950734170074</v>
       </c>
       <c r="C30">
-        <v>11.99568823477167</v>
+        <v>11.24781918274495</v>
       </c>
       <c r="D30">
-        <v>20.50608823477167</v>
+        <v>20.15251918274495</v>
       </c>
       <c r="E30">
-        <v>3.610400000000002</v>
+        <v>4.004700000000001</v>
       </c>
       <c r="F30">
-        <v>11.0404</v>
+        <v>11.4347</v>
       </c>
       <c r="G30">
         <v>2.53</v>
@@ -3735,37 +3735,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M30">
-        <v>2.60332632</v>
+        <v>2.69630226</v>
       </c>
       <c r="N30">
-        <v>-1.94332632</v>
+        <v>-2.03630226</v>
       </c>
       <c r="O30">
-        <v>-0.4663983168</v>
+        <v>-0.4887125424000001</v>
       </c>
       <c r="P30">
-        <v>-1.4769280032</v>
+        <v>-1.5475897176</v>
       </c>
       <c r="Q30">
-        <v>0.5030719967999999</v>
+        <v>0.4324102823999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1279004432902401</v>
+        <v>0.1290567875619336</v>
       </c>
       <c r="T30">
-        <v>1.1301435049061</v>
+        <v>1.146061019059707</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.06084523433850583</v>
+        <v>0.05874712280959183</v>
       </c>
       <c r="W30">
-        <v>0.2214526937429803</v>
+        <v>0.2219474284414983</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2535218097437743</v>
+        <v>0.2447796783732993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1559950734170073</v>
+        <v>0.1578950734170073</v>
       </c>
       <c r="C31">
-        <v>11.24781918274496</v>
+        <v>10.51193604907081</v>
       </c>
       <c r="D31">
-        <v>20.15251918274496</v>
+        <v>19.81093604907081</v>
       </c>
       <c r="E31">
-        <v>4.0047</v>
+        <v>4.398999999999999</v>
       </c>
       <c r="F31">
-        <v>11.4347</v>
+        <v>11.829</v>
       </c>
       <c r="G31">
         <v>2.53</v>
@@ -3817,37 +3817,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M31">
-        <v>2.69630226</v>
+        <v>2.7892782</v>
       </c>
       <c r="N31">
-        <v>-2.03630226</v>
+        <v>-2.1292782</v>
       </c>
       <c r="O31">
-        <v>-0.4887125423999999</v>
+        <v>-0.5110267679999999</v>
       </c>
       <c r="P31">
-        <v>-1.5475897176</v>
+        <v>-1.618251432</v>
       </c>
       <c r="Q31">
-        <v>0.4324102824000002</v>
+        <v>0.3617485679999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1290567875619336</v>
+        <v>0.1302461702413898</v>
       </c>
       <c r="T31">
-        <v>1.146061019059707</v>
+        <v>1.162433319331988</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05874712280959184</v>
+        <v>0.05678888538260544</v>
       </c>
       <c r="W31">
-        <v>0.2219474284414983</v>
+        <v>0.2224091808267817</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2447796783732994</v>
+        <v>0.236620355760856</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1578950734170073</v>
+        <v>0.1597950734170073</v>
       </c>
       <c r="C32">
-        <v>10.51193604907081</v>
+        <v>9.787439511931522</v>
       </c>
       <c r="D32">
-        <v>19.81093604907081</v>
+        <v>19.48073951193152</v>
       </c>
       <c r="E32">
-        <v>4.398999999999999</v>
+        <v>4.7933</v>
       </c>
       <c r="F32">
-        <v>11.829</v>
+        <v>12.2233</v>
       </c>
       <c r="G32">
         <v>2.53</v>
@@ -3899,37 +3899,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M32">
-        <v>2.7892782</v>
+        <v>2.88225414</v>
       </c>
       <c r="N32">
-        <v>-2.1292782</v>
+        <v>-2.22225414</v>
       </c>
       <c r="O32">
-        <v>-0.5110267679999999</v>
+        <v>-0.5333409936</v>
       </c>
       <c r="P32">
-        <v>-1.618251432</v>
+        <v>-1.6889131464</v>
       </c>
       <c r="Q32">
-        <v>0.3617485679999999</v>
+        <v>0.2910868536</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1302461702413898</v>
+        <v>0.1314700277811201</v>
       </c>
       <c r="T32">
-        <v>1.162433319331988</v>
+        <v>1.179280179032452</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05678888538260544</v>
+        <v>0.0549569858541343</v>
       </c>
       <c r="W32">
-        <v>0.2224091808267817</v>
+        <v>0.2228411427355951</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.236620355760856</v>
+        <v>0.2289874410588929</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1597950734170073</v>
+        <v>0.1616950734170073</v>
       </c>
       <c r="C33">
-        <v>9.787439511931522</v>
+        <v>9.073769550971313</v>
       </c>
       <c r="D33">
-        <v>19.48073951193152</v>
+        <v>19.16136955097131</v>
       </c>
       <c r="E33">
-        <v>4.7933</v>
+        <v>5.1876</v>
       </c>
       <c r="F33">
-        <v>12.2233</v>
+        <v>12.6176</v>
       </c>
       <c r="G33">
         <v>2.53</v>
@@ -3981,37 +3981,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M33">
-        <v>2.88225414</v>
+        <v>2.97523008</v>
       </c>
       <c r="N33">
-        <v>-2.22225414</v>
+        <v>-2.31523008</v>
       </c>
       <c r="O33">
-        <v>-0.5333409936</v>
+        <v>-0.5556552191999999</v>
       </c>
       <c r="P33">
-        <v>-1.6889131464</v>
+        <v>-1.7595748608</v>
       </c>
       <c r="Q33">
-        <v>0.2910868536</v>
+        <v>0.2204251392000003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1314700277811201</v>
+        <v>0.1327298811308424</v>
       </c>
       <c r="T33">
-        <v>1.179280179032452</v>
+        <v>1.196622534606459</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0549569858541343</v>
+        <v>0.05323958004619261</v>
       </c>
       <c r="W33">
-        <v>0.2228411427355951</v>
+        <v>0.2232461070251078</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2289874410588929</v>
+        <v>0.2218315835258026</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1616950734170073</v>
+        <v>0.1635950734170073</v>
       </c>
       <c r="C34">
-        <v>9.073769550971313</v>
+        <v>8.370402277691031</v>
       </c>
       <c r="D34">
-        <v>19.16136955097131</v>
+        <v>18.85230227769103</v>
       </c>
       <c r="E34">
-        <v>5.1876</v>
+        <v>5.581900000000001</v>
       </c>
       <c r="F34">
-        <v>12.6176</v>
+        <v>13.0119</v>
       </c>
       <c r="G34">
         <v>2.53</v>
@@ -4063,37 +4063,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M34">
-        <v>2.97523008</v>
+        <v>3.06820602</v>
       </c>
       <c r="N34">
-        <v>-2.31523008</v>
+        <v>-2.40820602</v>
       </c>
       <c r="O34">
-        <v>-0.5556552191999999</v>
+        <v>-0.5779694448</v>
       </c>
       <c r="P34">
-        <v>-1.7595748608</v>
+        <v>-1.8302365752</v>
       </c>
       <c r="Q34">
-        <v>0.2204251392000003</v>
+        <v>0.1497634247999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1327298811308424</v>
+        <v>0.134027342043243</v>
       </c>
       <c r="T34">
-        <v>1.196622534606459</v>
+        <v>1.214482572436406</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.05323958004619261</v>
+        <v>0.05162625943873222</v>
       </c>
       <c r="W34">
-        <v>0.2232461070251078</v>
+        <v>0.223626528024347</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2218315835258026</v>
+        <v>0.2151094143280509</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1635950734170073</v>
+        <v>0.1654950734170073</v>
       </c>
       <c r="C35">
-        <v>8.370402277691031</v>
+        <v>7.676847067722433</v>
       </c>
       <c r="D35">
-        <v>18.85230227769103</v>
+        <v>18.55304706772243</v>
       </c>
       <c r="E35">
-        <v>5.581900000000001</v>
+        <v>5.9762</v>
       </c>
       <c r="F35">
-        <v>13.0119</v>
+        <v>13.4062</v>
       </c>
       <c r="G35">
         <v>2.53</v>
@@ -4145,37 +4145,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M35">
-        <v>3.06820602</v>
+        <v>3.16118196</v>
       </c>
       <c r="N35">
-        <v>-2.40820602</v>
+        <v>-2.50118196</v>
       </c>
       <c r="O35">
-        <v>-0.5779694448</v>
+        <v>-0.6002836704</v>
       </c>
       <c r="P35">
-        <v>-1.8302365752</v>
+        <v>-1.9008982896</v>
       </c>
       <c r="Q35">
-        <v>0.1497634247999997</v>
+        <v>0.07910171040000025</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.134027342043243</v>
+        <v>0.1353641199529892</v>
       </c>
       <c r="T35">
-        <v>1.214482572436406</v>
+        <v>1.232883823533927</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05162625943873222</v>
+        <v>0.0501078400434754</v>
       </c>
       <c r="W35">
-        <v>0.223626528024347</v>
+        <v>0.2239845713177485</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2151094143280509</v>
+        <v>0.2087826668478141</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1654950734170073</v>
+        <v>0.1673950734170073</v>
       </c>
       <c r="C36">
-        <v>7.676847067722433</v>
+        <v>6.992643961962704</v>
       </c>
       <c r="D36">
-        <v>18.55304706772243</v>
+        <v>18.2631439619627</v>
       </c>
       <c r="E36">
-        <v>5.9762</v>
+        <v>6.370500000000002</v>
       </c>
       <c r="F36">
-        <v>13.4062</v>
+        <v>13.8005</v>
       </c>
       <c r="G36">
         <v>2.53</v>
@@ -4227,37 +4227,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M36">
-        <v>3.16118196</v>
+        <v>3.2541579</v>
       </c>
       <c r="N36">
-        <v>-2.50118196</v>
+        <v>-2.5941579</v>
       </c>
       <c r="O36">
-        <v>-0.6002836704</v>
+        <v>-0.622597896</v>
       </c>
       <c r="P36">
-        <v>-1.9008982896</v>
+        <v>-1.971560004</v>
       </c>
       <c r="Q36">
-        <v>0.07910171040000025</v>
+        <v>0.008439995999999672</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1353641199529892</v>
+        <v>0.1367420294907274</v>
       </c>
       <c r="T36">
-        <v>1.232883823533927</v>
+        <v>1.25185126697291</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0501078400434754</v>
+        <v>0.04867618747080466</v>
       </c>
       <c r="W36">
-        <v>0.2239845713177485</v>
+        <v>0.2243221549943843</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2087826668478141</v>
+        <v>0.2028174477950194</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1673950734170073</v>
+        <v>0.1692950734170073</v>
       </c>
       <c r="C37">
-        <v>6.992643961962704</v>
+        <v>6.317361307613751</v>
       </c>
       <c r="D37">
-        <v>18.2631439619627</v>
+        <v>17.98216130761375</v>
       </c>
       <c r="E37">
-        <v>6.370500000000002</v>
+        <v>6.764800000000001</v>
       </c>
       <c r="F37">
-        <v>13.8005</v>
+        <v>14.1948</v>
       </c>
       <c r="G37">
         <v>2.53</v>
@@ -4309,37 +4309,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M37">
-        <v>3.2541579</v>
+        <v>3.34713384</v>
       </c>
       <c r="N37">
-        <v>-2.5941579</v>
+        <v>-2.68713384</v>
       </c>
       <c r="O37">
-        <v>-0.622597896</v>
+        <v>-0.6449121216</v>
       </c>
       <c r="P37">
-        <v>-1.971560004</v>
+        <v>-2.0422217184</v>
       </c>
       <c r="Q37">
-        <v>0.008439995999999672</v>
+        <v>-0.06222171840000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1367420294907274</v>
+        <v>0.1381629987015201</v>
       </c>
       <c r="T37">
-        <v>1.25185126697291</v>
+        <v>1.271411443019362</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04867618747080466</v>
+        <v>0.0473240711521712</v>
       </c>
       <c r="W37">
-        <v>0.2243221549943843</v>
+        <v>0.2246409840223181</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2028174477950194</v>
+        <v>0.1971836298007134</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1692950734170073</v>
+        <v>0.1711950734170073</v>
       </c>
       <c r="C38">
-        <v>6.317361307613753</v>
+        <v>5.650593613680952</v>
       </c>
       <c r="D38">
-        <v>17.98216130761375</v>
+        <v>17.70969361368095</v>
       </c>
       <c r="E38">
-        <v>6.764799999999999</v>
+        <v>7.1591</v>
       </c>
       <c r="F38">
-        <v>14.1948</v>
+        <v>14.5891</v>
       </c>
       <c r="G38">
         <v>2.53</v>
@@ -4391,37 +4391,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M38">
-        <v>3.34713384</v>
+        <v>3.44010978</v>
       </c>
       <c r="N38">
-        <v>-2.68713384</v>
+        <v>-2.78010978</v>
       </c>
       <c r="O38">
-        <v>-0.6449121215999999</v>
+        <v>-0.6672263472</v>
       </c>
       <c r="P38">
-        <v>-2.0422217184</v>
+        <v>-2.1128834328</v>
       </c>
       <c r="Q38">
-        <v>-0.06222171839999957</v>
+        <v>-0.1328834328000004</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.13816299870152</v>
+        <v>0.1396290780459886</v>
       </c>
       <c r="T38">
-        <v>1.271411443019362</v>
+        <v>1.291592577035543</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04732407115217121</v>
+        <v>0.04604504220211252</v>
       </c>
       <c r="W38">
-        <v>0.2246409840223181</v>
+        <v>0.2249425790487419</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1971836298007134</v>
+        <v>0.1918543425088022</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1711950734170073</v>
+        <v>0.1730950734170073</v>
       </c>
       <c r="C39">
-        <v>5.650593613680952</v>
+        <v>4.991959598524183</v>
       </c>
       <c r="D39">
-        <v>17.70969361368095</v>
+        <v>17.44535959852418</v>
       </c>
       <c r="E39">
-        <v>7.1591</v>
+        <v>7.5534</v>
       </c>
       <c r="F39">
-        <v>14.5891</v>
+        <v>14.9834</v>
       </c>
       <c r="G39">
         <v>2.53</v>
@@ -4473,37 +4473,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M39">
-        <v>3.44010978</v>
+        <v>3.53308572</v>
       </c>
       <c r="N39">
-        <v>-2.78010978</v>
+        <v>-2.87308572</v>
       </c>
       <c r="O39">
-        <v>-0.6672263472</v>
+        <v>-0.6895405727999999</v>
       </c>
       <c r="P39">
-        <v>-2.1128834328</v>
+        <v>-2.1835451472</v>
       </c>
       <c r="Q39">
-        <v>-0.1328834328000004</v>
+        <v>-0.2035451471999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1396290780459886</v>
+        <v>0.1411424502725368</v>
       </c>
       <c r="T39">
-        <v>1.291592577035543</v>
+        <v>1.312424715374825</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04604504220211252</v>
+        <v>0.04483333056521482</v>
       </c>
       <c r="W39">
-        <v>0.2249425790487419</v>
+        <v>0.2252283006527223</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1918543425088022</v>
+        <v>0.1868055440217284</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1730950734170073</v>
+        <v>0.1749950734170073</v>
       </c>
       <c r="C40">
-        <v>4.991959598524183</v>
+        <v>4.341100409690338</v>
       </c>
       <c r="D40">
-        <v>17.44535959852418</v>
+        <v>17.18880040969034</v>
       </c>
       <c r="E40">
-        <v>7.5534</v>
+        <v>7.947700000000001</v>
       </c>
       <c r="F40">
-        <v>14.9834</v>
+        <v>15.3777</v>
       </c>
       <c r="G40">
         <v>2.53</v>
@@ -4555,37 +4555,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M40">
-        <v>3.53308572</v>
+        <v>3.62606166</v>
       </c>
       <c r="N40">
-        <v>-2.87308572</v>
+        <v>-2.96606166</v>
       </c>
       <c r="O40">
-        <v>-0.6895405727999999</v>
+        <v>-0.7118547984</v>
       </c>
       <c r="P40">
-        <v>-2.1835451472</v>
+        <v>-2.2542068616</v>
       </c>
       <c r="Q40">
-        <v>-0.2035451471999998</v>
+        <v>-0.2742068616000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1411424502725368</v>
+        <v>0.1427054412606112</v>
       </c>
       <c r="T40">
-        <v>1.312424715374825</v>
+        <v>1.333939874643265</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04483333056521482</v>
+        <v>0.04368375798661957</v>
       </c>
       <c r="W40">
-        <v>0.2252283006527223</v>
+        <v>0.2254993698667551</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1868055440217284</v>
+        <v>0.1820156582775816</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1749950734170073</v>
+        <v>0.1768950734170073</v>
       </c>
       <c r="C41">
-        <v>4.341100409690338</v>
+        <v>3.697677998548878</v>
       </c>
       <c r="D41">
-        <v>17.18880040969034</v>
+        <v>16.93967799854888</v>
       </c>
       <c r="E41">
-        <v>7.947700000000001</v>
+        <v>8.342000000000001</v>
       </c>
       <c r="F41">
-        <v>15.3777</v>
+        <v>15.772</v>
       </c>
       <c r="G41">
         <v>2.53</v>
@@ -4637,37 +4637,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M41">
-        <v>3.62606166</v>
+        <v>3.7190376</v>
       </c>
       <c r="N41">
-        <v>-2.96606166</v>
+        <v>-3.0590376</v>
       </c>
       <c r="O41">
-        <v>-0.7118547984</v>
+        <v>-0.7341690239999999</v>
       </c>
       <c r="P41">
-        <v>-2.2542068616</v>
+        <v>-2.324868576</v>
       </c>
       <c r="Q41">
-        <v>-0.2742068616000002</v>
+        <v>-0.3448685760000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1427054412606112</v>
+        <v>0.1443205319482881</v>
       </c>
       <c r="T41">
-        <v>1.333939874643265</v>
+        <v>1.35617220588732</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04368375798661957</v>
+        <v>0.04259166403695408</v>
       </c>
       <c r="W41">
-        <v>0.2254993698667551</v>
+        <v>0.2257568856200862</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1820156582775816</v>
+        <v>0.177465266820642</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1768950734170073</v>
+        <v>0.1787950734170073</v>
       </c>
       <c r="C42">
-        <v>3.697677998548878</v>
+        <v>3.061373634249417</v>
       </c>
       <c r="D42">
-        <v>16.93967799854888</v>
+        <v>16.69767363424942</v>
       </c>
       <c r="E42">
-        <v>8.342000000000001</v>
+        <v>8.7363</v>
       </c>
       <c r="F42">
-        <v>15.772</v>
+        <v>16.1663</v>
       </c>
       <c r="G42">
         <v>2.53</v>
@@ -4719,37 +4719,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M42">
-        <v>3.7190376</v>
+        <v>3.81201354</v>
       </c>
       <c r="N42">
-        <v>-3.0590376</v>
+        <v>-3.15201354</v>
       </c>
       <c r="O42">
-        <v>-0.7341690239999999</v>
+        <v>-0.7564832496</v>
       </c>
       <c r="P42">
-        <v>-2.324868576</v>
+        <v>-2.3955302904</v>
       </c>
       <c r="Q42">
-        <v>-0.3448685760000001</v>
+        <v>-0.4155302904</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1443205319482881</v>
+        <v>0.1459903714728353</v>
       </c>
       <c r="T42">
-        <v>1.35617220588732</v>
+        <v>1.37915817547863</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04259166403695408</v>
+        <v>0.04155284296288203</v>
       </c>
       <c r="W42">
-        <v>0.2257568856200862</v>
+        <v>0.2260018396293524</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.177465266820642</v>
+        <v>0.1731368456786752</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1787950734170073</v>
+        <v>0.1806950734170073</v>
       </c>
       <c r="C43">
-        <v>3.061373634249417</v>
+        <v>2.431886543265016</v>
       </c>
       <c r="D43">
-        <v>16.69767363424942</v>
+        <v>16.46248654326502</v>
       </c>
       <c r="E43">
-        <v>8.7363</v>
+        <v>9.130600000000001</v>
       </c>
       <c r="F43">
-        <v>16.1663</v>
+        <v>16.5606</v>
       </c>
       <c r="G43">
         <v>2.53</v>
@@ -4801,37 +4801,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M43">
-        <v>3.81201354</v>
+        <v>3.90498948</v>
       </c>
       <c r="N43">
-        <v>-3.15201354</v>
+        <v>-3.24498948</v>
       </c>
       <c r="O43">
-        <v>-0.7564832496</v>
+        <v>-0.7787974752</v>
       </c>
       <c r="P43">
-        <v>-2.3955302904</v>
+        <v>-2.4661920048</v>
       </c>
       <c r="Q43">
-        <v>-0.4155302904</v>
+        <v>-0.4861920047999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1459903714728353</v>
+        <v>0.1477177916706428</v>
       </c>
       <c r="T43">
-        <v>1.37915817547863</v>
+        <v>1.40293676471102</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04155284296288203</v>
+        <v>0.04056348955900389</v>
       </c>
       <c r="W43">
-        <v>0.2260018396293524</v>
+        <v>0.2262351291619869</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1731368456786752</v>
+        <v>0.1690145398291829</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1806950734170073</v>
+        <v>0.1825950734170074</v>
       </c>
       <c r="C44">
-        <v>2.431886543265016</v>
+        <v>1.808932662310884</v>
       </c>
       <c r="D44">
-        <v>16.46248654326502</v>
+        <v>16.23383266231088</v>
       </c>
       <c r="E44">
-        <v>9.130600000000001</v>
+        <v>9.524899999999999</v>
       </c>
       <c r="F44">
-        <v>16.5606</v>
+        <v>16.9549</v>
       </c>
       <c r="G44">
         <v>2.53</v>
@@ -4883,37 +4883,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M44">
-        <v>3.90498948</v>
+        <v>3.99796542</v>
       </c>
       <c r="N44">
-        <v>-3.24498948</v>
+        <v>-3.33796542</v>
       </c>
       <c r="O44">
-        <v>-0.7787974752</v>
+        <v>-0.8011117007999999</v>
       </c>
       <c r="P44">
-        <v>-2.4661920048</v>
+        <v>-2.5368537192</v>
       </c>
       <c r="Q44">
-        <v>-0.4861920047999999</v>
+        <v>-0.5568537191999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1477177916706428</v>
+        <v>0.1495058231034611</v>
       </c>
       <c r="T44">
-        <v>1.40293676471102</v>
+        <v>1.427549690407705</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04056348955900389</v>
+        <v>0.03962015259251543</v>
       </c>
       <c r="W44">
-        <v>0.2262351291619869</v>
+        <v>0.2264575680186849</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1690145398291829</v>
+        <v>0.165083969135481</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1825950734170074</v>
+        <v>0.1844950734170074</v>
       </c>
       <c r="C45">
-        <v>1.808932662310884</v>
+        <v>1.192243493766643</v>
       </c>
       <c r="D45">
-        <v>16.23383266231088</v>
+        <v>16.01144349376664</v>
       </c>
       <c r="E45">
-        <v>9.524899999999999</v>
+        <v>9.9192</v>
       </c>
       <c r="F45">
-        <v>16.9549</v>
+        <v>17.3492</v>
       </c>
       <c r="G45">
         <v>2.53</v>
@@ -4965,37 +4965,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M45">
-        <v>3.99796542</v>
+        <v>4.09094136</v>
       </c>
       <c r="N45">
-        <v>-3.33796542</v>
+        <v>-3.43094136</v>
       </c>
       <c r="O45">
-        <v>-0.8011117007999999</v>
+        <v>-0.8234259264</v>
       </c>
       <c r="P45">
-        <v>-2.5368537192</v>
+        <v>-2.6075154336</v>
       </c>
       <c r="Q45">
-        <v>-0.5568537191999998</v>
+        <v>-0.6275154336000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1495058231034611</v>
+        <v>0.1513577128017372</v>
       </c>
       <c r="T45">
-        <v>1.427549690407705</v>
+        <v>1.453041649164985</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03962015259251543</v>
+        <v>0.03871969457904916</v>
       </c>
       <c r="W45">
-        <v>0.2264575680186849</v>
+        <v>0.2266698960182602</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.165083969135481</v>
+        <v>0.1613320607460382</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1844950734170074</v>
+        <v>0.1863950734170073</v>
       </c>
       <c r="C46">
-        <v>1.192243493766643</v>
+        <v>0.5815650539053472</v>
       </c>
       <c r="D46">
-        <v>16.01144349376664</v>
+        <v>15.79506505390535</v>
       </c>
       <c r="E46">
-        <v>9.9192</v>
+        <v>10.3135</v>
       </c>
       <c r="F46">
-        <v>17.3492</v>
+        <v>17.7435</v>
       </c>
       <c r="G46">
         <v>2.53</v>
@@ -5047,37 +5047,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M46">
-        <v>4.09094136</v>
+        <v>4.1839173</v>
       </c>
       <c r="N46">
-        <v>-3.43094136</v>
+        <v>-3.5239173</v>
       </c>
       <c r="O46">
-        <v>-0.8234259264</v>
+        <v>-0.845740152</v>
       </c>
       <c r="P46">
-        <v>-2.6075154336</v>
+        <v>-2.678177148</v>
       </c>
       <c r="Q46">
-        <v>-0.6275154336000002</v>
+        <v>-0.6981771480000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1513577128017372</v>
+        <v>0.153276943943587</v>
       </c>
       <c r="T46">
-        <v>1.453041649164985</v>
+        <v>1.479460588240712</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03871969457904916</v>
+        <v>0.03785925692173697</v>
       </c>
       <c r="W46">
-        <v>0.2266698960182602</v>
+        <v>0.2268727872178544</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1613320607460382</v>
+        <v>0.1577469038405707</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1863950734170073</v>
+        <v>0.1882950734170074</v>
       </c>
       <c r="C47">
-        <v>0.5815650539053472</v>
+        <v>-0.02334309473285856</v>
       </c>
       <c r="D47">
-        <v>15.79506505390535</v>
+        <v>15.58445690526714</v>
       </c>
       <c r="E47">
-        <v>10.3135</v>
+        <v>10.7078</v>
       </c>
       <c r="F47">
-        <v>17.7435</v>
+        <v>18.1378</v>
       </c>
       <c r="G47">
         <v>2.53</v>
@@ -5129,37 +5129,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M47">
-        <v>4.1839173</v>
+        <v>4.276893240000001</v>
       </c>
       <c r="N47">
-        <v>-3.5239173</v>
+        <v>-3.61689324</v>
       </c>
       <c r="O47">
-        <v>-0.845740152</v>
+        <v>-0.8680543776</v>
       </c>
       <c r="P47">
-        <v>-2.678177148</v>
+        <v>-2.7488388624</v>
       </c>
       <c r="Q47">
-        <v>-0.6981771480000001</v>
+        <v>-0.7688388624000004</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.153276943943587</v>
+        <v>0.1552672577203201</v>
       </c>
       <c r="T47">
-        <v>1.479460588240712</v>
+        <v>1.506858006541466</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03785925692173697</v>
+        <v>0.03703622959735137</v>
       </c>
       <c r="W47">
-        <v>0.2268727872178544</v>
+        <v>0.2270668570609445</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1577469038405707</v>
+        <v>0.1543176233222974</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1882950734170074</v>
+        <v>0.1901950734170073</v>
       </c>
       <c r="C48">
-        <v>-0.02334309473285856</v>
+        <v>-0.6227087345728854</v>
       </c>
       <c r="D48">
-        <v>15.58445690526714</v>
+        <v>15.37939126542711</v>
       </c>
       <c r="E48">
-        <v>10.7078</v>
+        <v>11.1021</v>
       </c>
       <c r="F48">
-        <v>18.1378</v>
+        <v>18.5321</v>
       </c>
       <c r="G48">
         <v>2.53</v>
@@ -5211,37 +5211,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M48">
-        <v>4.276893240000001</v>
+        <v>4.36986918</v>
       </c>
       <c r="N48">
-        <v>-3.61689324</v>
+        <v>-3.70986918</v>
       </c>
       <c r="O48">
-        <v>-0.8680543776</v>
+        <v>-0.8903686032</v>
       </c>
       <c r="P48">
-        <v>-2.7488388624</v>
+        <v>-2.8195005768</v>
       </c>
       <c r="Q48">
-        <v>-0.7688388624000004</v>
+        <v>-0.8395005768000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1552672577203201</v>
+        <v>0.1573326776773072</v>
       </c>
       <c r="T48">
-        <v>1.506858006541466</v>
+        <v>1.535289289683758</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03703622959735137</v>
+        <v>0.03624822471230135</v>
       </c>
       <c r="W48">
-        <v>0.2270668570609445</v>
+        <v>0.2272526686128394</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1543176233222974</v>
+        <v>0.151034269634589</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1901950734170073</v>
+        <v>0.1920950734170073</v>
       </c>
       <c r="C49">
-        <v>-0.6227087345728854</v>
+        <v>-1.216747814787976</v>
       </c>
       <c r="D49">
-        <v>15.37939126542711</v>
+        <v>15.17965218521202</v>
       </c>
       <c r="E49">
-        <v>11.1021</v>
+        <v>11.4964</v>
       </c>
       <c r="F49">
-        <v>18.5321</v>
+        <v>18.9264</v>
       </c>
       <c r="G49">
         <v>2.53</v>
@@ -5293,37 +5293,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M49">
-        <v>4.36986918</v>
+        <v>4.462845120000001</v>
       </c>
       <c r="N49">
-        <v>-3.70986918</v>
+        <v>-3.802845120000001</v>
       </c>
       <c r="O49">
-        <v>-0.8903686032</v>
+        <v>-0.9126828288000001</v>
       </c>
       <c r="P49">
-        <v>-2.8195005768</v>
+        <v>-2.890162291200001</v>
       </c>
       <c r="Q49">
-        <v>-0.8395005768000003</v>
+        <v>-0.9101622912000007</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1573326776773072</v>
+        <v>0.1594775368634093</v>
       </c>
       <c r="T49">
-        <v>1.535289289683758</v>
+        <v>1.564814083716138</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03624822471230135</v>
+        <v>0.0354930533641284</v>
       </c>
       <c r="W49">
-        <v>0.2272526686128394</v>
+        <v>0.2274307380167385</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.151034269634589</v>
+        <v>0.147887722350535</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1920950734170073</v>
+        <v>0.1939950734170073</v>
       </c>
       <c r="C50">
-        <v>-1.216747814787972</v>
+        <v>-1.805665209866596</v>
       </c>
       <c r="D50">
-        <v>15.17965218521202</v>
+        <v>14.9850347901334</v>
       </c>
       <c r="E50">
-        <v>11.4964</v>
+        <v>11.8907</v>
       </c>
       <c r="F50">
-        <v>18.9264</v>
+        <v>19.3207</v>
       </c>
       <c r="G50">
         <v>2.53</v>
@@ -5375,37 +5375,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M50">
-        <v>4.46284512</v>
+        <v>4.55582106</v>
       </c>
       <c r="N50">
-        <v>-3.80284512</v>
+        <v>-3.895821059999999</v>
       </c>
       <c r="O50">
-        <v>-0.9126828288</v>
+        <v>-0.9349970543999998</v>
       </c>
       <c r="P50">
-        <v>-2.8901622912</v>
+        <v>-2.9608240056</v>
       </c>
       <c r="Q50">
-        <v>-0.9101622911999998</v>
+        <v>-0.9808240055999997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1594775368634093</v>
+        <v>0.1617065081744566</v>
       </c>
       <c r="T50">
-        <v>1.564814083716138</v>
+        <v>1.595496712808611</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0354930533641284</v>
+        <v>0.03476870533628906</v>
       </c>
       <c r="W50">
-        <v>0.2274307380167385</v>
+        <v>0.227601539281703</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.147887722350535</v>
+        <v>0.1448696055678711</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1939950734170073</v>
+        <v>0.1958950734170073</v>
       </c>
       <c r="C51">
-        <v>-1.805665209866596</v>
+        <v>-2.389655420564928</v>
       </c>
       <c r="D51">
-        <v>14.9850347901334</v>
+        <v>14.79534457943507</v>
       </c>
       <c r="E51">
-        <v>11.8907</v>
+        <v>12.285</v>
       </c>
       <c r="F51">
-        <v>19.3207</v>
+        <v>19.715</v>
       </c>
       <c r="G51">
         <v>2.53</v>
@@ -5457,37 +5457,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M51">
-        <v>4.55582106</v>
+        <v>4.648797</v>
       </c>
       <c r="N51">
-        <v>-3.895821059999999</v>
+        <v>-3.988797</v>
       </c>
       <c r="O51">
-        <v>-0.9349970543999998</v>
+        <v>-0.95731128</v>
       </c>
       <c r="P51">
-        <v>-2.9608240056</v>
+        <v>-3.03148572</v>
       </c>
       <c r="Q51">
-        <v>-0.9808240055999997</v>
+        <v>-1.05148572</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1617065081744566</v>
+        <v>0.1640246383379457</v>
       </c>
       <c r="T51">
-        <v>1.595496712808611</v>
+        <v>1.627406647064784</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03476870533628906</v>
+        <v>0.03407333122956327</v>
       </c>
       <c r="W51">
-        <v>0.227601539281703</v>
+        <v>0.227765508496069</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1448696055678711</v>
+        <v>0.1419722134565136</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1958950734170073</v>
+        <v>0.1977950734170073</v>
       </c>
       <c r="C52">
-        <v>-2.389655420564928</v>
+        <v>-2.968903222286119</v>
       </c>
       <c r="D52">
-        <v>14.79534457943507</v>
+        <v>14.61039677771388</v>
       </c>
       <c r="E52">
-        <v>12.285</v>
+        <v>12.6793</v>
       </c>
       <c r="F52">
-        <v>19.715</v>
+        <v>20.1093</v>
       </c>
       <c r="G52">
         <v>2.53</v>
@@ -5539,37 +5539,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M52">
-        <v>4.648797</v>
+        <v>4.741772940000001</v>
       </c>
       <c r="N52">
-        <v>-3.988797</v>
+        <v>-4.08177294</v>
       </c>
       <c r="O52">
-        <v>-0.95731128</v>
+        <v>-0.9796255056000001</v>
       </c>
       <c r="P52">
-        <v>-3.03148572</v>
+        <v>-3.1021474344</v>
       </c>
       <c r="Q52">
-        <v>-1.05148572</v>
+        <v>-1.1221474344</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1640246383379457</v>
+        <v>0.1664373860591283</v>
       </c>
       <c r="T52">
-        <v>1.627406647064784</v>
+        <v>1.660619027617126</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03407333122956327</v>
+        <v>0.03340522669565026</v>
       </c>
       <c r="W52">
-        <v>0.227765508496069</v>
+        <v>0.2279230475451657</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1419722134565136</v>
+        <v>0.1391884445652094</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1977950734170073</v>
+        <v>0.1996950734170073</v>
       </c>
       <c r="C53">
-        <v>-2.968903222286119</v>
+        <v>-3.543584265429953</v>
       </c>
       <c r="D53">
-        <v>14.61039677771388</v>
+        <v>14.43001573457005</v>
       </c>
       <c r="E53">
-        <v>12.6793</v>
+        <v>13.0736</v>
       </c>
       <c r="F53">
-        <v>20.1093</v>
+        <v>20.5036</v>
       </c>
       <c r="G53">
         <v>2.53</v>
@@ -5621,37 +5621,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M53">
-        <v>4.741772940000001</v>
+        <v>4.834748880000001</v>
       </c>
       <c r="N53">
-        <v>-4.08177294</v>
+        <v>-4.174748880000001</v>
       </c>
       <c r="O53">
-        <v>-0.9796255056000001</v>
+        <v>-1.0019397312</v>
       </c>
       <c r="P53">
-        <v>-3.1021474344</v>
+        <v>-3.172809148800001</v>
       </c>
       <c r="Q53">
-        <v>-1.1221474344</v>
+        <v>-1.192809148800001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1664373860591283</v>
+        <v>0.1689506649353601</v>
       </c>
       <c r="T53">
-        <v>1.660619027617126</v>
+        <v>1.695215257359149</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03340522669565026</v>
+        <v>0.03276281848996467</v>
       </c>
       <c r="W53">
-        <v>0.2279230475451657</v>
+        <v>0.2280745274000663</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1391884445652094</v>
+        <v>0.1365117437081862</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1996950734170073</v>
+        <v>0.2015950734170074</v>
       </c>
       <c r="C54">
-        <v>-3.543584265429953</v>
+        <v>-4.11386563181307</v>
       </c>
       <c r="D54">
-        <v>14.43001573457005</v>
+        <v>14.25403436818693</v>
       </c>
       <c r="E54">
-        <v>13.0736</v>
+        <v>13.4679</v>
       </c>
       <c r="F54">
-        <v>20.5036</v>
+        <v>20.8979</v>
       </c>
       <c r="G54">
         <v>2.53</v>
@@ -5703,37 +5703,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M54">
-        <v>4.834748880000001</v>
+        <v>4.92772482</v>
       </c>
       <c r="N54">
-        <v>-4.174748880000001</v>
+        <v>-4.26772482</v>
       </c>
       <c r="O54">
-        <v>-1.0019397312</v>
+        <v>-1.0242539568</v>
       </c>
       <c r="P54">
-        <v>-3.172809148800001</v>
+        <v>-3.2434708632</v>
       </c>
       <c r="Q54">
-        <v>-1.192809148800001</v>
+        <v>-1.2634708632</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1689506649353601</v>
+        <v>0.1715708918488784</v>
       </c>
       <c r="T54">
-        <v>1.695215257359149</v>
+        <v>1.731283667090196</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03276281848996467</v>
+        <v>0.03214465210336157</v>
       </c>
       <c r="W54">
-        <v>0.2280745274000663</v>
+        <v>0.2282202910340274</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1365117437081862</v>
+        <v>0.1339360504306732</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2015950734170074</v>
+        <v>0.2034950734170073</v>
       </c>
       <c r="C55">
-        <v>-4.11386563181307</v>
+        <v>-4.679906350864815</v>
       </c>
       <c r="D55">
-        <v>14.25403436818693</v>
+        <v>14.08229364913518</v>
       </c>
       <c r="E55">
-        <v>13.4679</v>
+        <v>13.8622</v>
       </c>
       <c r="F55">
-        <v>20.8979</v>
+        <v>21.2922</v>
       </c>
       <c r="G55">
         <v>2.53</v>
@@ -5785,37 +5785,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M55">
-        <v>4.92772482</v>
+        <v>5.02070076</v>
       </c>
       <c r="N55">
-        <v>-4.26772482</v>
+        <v>-4.36070076</v>
       </c>
       <c r="O55">
-        <v>-1.0242539568</v>
+        <v>-1.0465681824</v>
       </c>
       <c r="P55">
-        <v>-3.2434708632</v>
+        <v>-3.314132577600001</v>
       </c>
       <c r="Q55">
-        <v>-1.2634708632</v>
+        <v>-1.334132577600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1715708918488784</v>
+        <v>0.1743050416716801</v>
       </c>
       <c r="T55">
-        <v>1.731283667090196</v>
+        <v>1.768920268548678</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03214465210336157</v>
+        <v>0.03154938076811414</v>
       </c>
       <c r="W55">
-        <v>0.2282202910340274</v>
+        <v>0.2283606560148787</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1339360504306732</v>
+        <v>0.1314557532004755</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2034950734170073</v>
+        <v>0.2053950734170074</v>
       </c>
       <c r="C56">
-        <v>-4.679906350864815</v>
+        <v>-5.241857878950807</v>
       </c>
       <c r="D56">
-        <v>14.08229364913518</v>
+        <v>13.91464212104919</v>
       </c>
       <c r="E56">
-        <v>13.8622</v>
+        <v>14.2565</v>
       </c>
       <c r="F56">
-        <v>21.2922</v>
+        <v>21.6865</v>
       </c>
       <c r="G56">
         <v>2.53</v>
@@ -5867,37 +5867,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M56">
-        <v>5.02070076</v>
+        <v>5.113676700000001</v>
       </c>
       <c r="N56">
-        <v>-4.36070076</v>
+        <v>-4.453676700000001</v>
       </c>
       <c r="O56">
-        <v>-1.0465681824</v>
+        <v>-1.068882408</v>
       </c>
       <c r="P56">
-        <v>-3.314132577600001</v>
+        <v>-3.384794292</v>
       </c>
       <c r="Q56">
-        <v>-1.334132577600001</v>
+        <v>-1.404794292</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1743050416716801</v>
+        <v>0.1771607092643841</v>
       </c>
       <c r="T56">
-        <v>1.768920268548678</v>
+        <v>1.80822960784976</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03154938076811414</v>
+        <v>0.03097575566323933</v>
       </c>
       <c r="W56">
-        <v>0.2283606560148787</v>
+        <v>0.2284959168146082</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1314557532004755</v>
+        <v>0.1290656485968306</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2053950734170074</v>
+        <v>0.2072950734170074</v>
       </c>
       <c r="C57">
-        <v>-5.241857878950807</v>
+        <v>-5.799864544860842</v>
       </c>
       <c r="D57">
-        <v>13.91464212104919</v>
+        <v>13.75093545513916</v>
       </c>
       <c r="E57">
-        <v>14.2565</v>
+        <v>14.6508</v>
       </c>
       <c r="F57">
-        <v>21.6865</v>
+        <v>22.0808</v>
       </c>
       <c r="G57">
         <v>2.53</v>
@@ -5949,37 +5949,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M57">
-        <v>5.113676700000001</v>
+        <v>5.206652640000001</v>
       </c>
       <c r="N57">
-        <v>-4.453676700000001</v>
+        <v>-4.54665264</v>
       </c>
       <c r="O57">
-        <v>-1.068882408</v>
+        <v>-1.0911966336</v>
       </c>
       <c r="P57">
-        <v>-3.384794292</v>
+        <v>-3.4554560064</v>
       </c>
       <c r="Q57">
-        <v>-1.404794292</v>
+        <v>-1.4754560064</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1771607092643841</v>
+        <v>0.1801461799294837</v>
       </c>
       <c r="T57">
-        <v>1.80822960784976</v>
+        <v>1.84932573530089</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03097575566323933</v>
+        <v>0.03042261716925292</v>
       </c>
       <c r="W57">
-        <v>0.2284959168146082</v>
+        <v>0.2286263468714902</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1290656485968306</v>
+        <v>0.1267609048718872</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2072950734170074</v>
+        <v>0.2091950734170073</v>
       </c>
       <c r="C58">
-        <v>-5.799864544860842</v>
+        <v>-6.354063964215328</v>
       </c>
       <c r="D58">
-        <v>13.75093545513916</v>
+        <v>13.59103603578467</v>
       </c>
       <c r="E58">
-        <v>14.6508</v>
+        <v>15.0451</v>
       </c>
       <c r="F58">
-        <v>22.0808</v>
+        <v>22.4751</v>
       </c>
       <c r="G58">
         <v>2.53</v>
@@ -6031,37 +6031,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M58">
-        <v>5.206652640000001</v>
+        <v>5.29962858</v>
       </c>
       <c r="N58">
-        <v>-4.54665264</v>
+        <v>-4.63962858</v>
       </c>
       <c r="O58">
-        <v>-1.0911966336</v>
+        <v>-1.1135108592</v>
       </c>
       <c r="P58">
-        <v>-3.4554560064</v>
+        <v>-3.5261177208</v>
       </c>
       <c r="Q58">
-        <v>-1.4754560064</v>
+        <v>-1.5461177208</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1801461799294837</v>
+        <v>0.1832705096952857</v>
       </c>
       <c r="T58">
-        <v>1.84932573530089</v>
+        <v>1.892333310540446</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03042261716925292</v>
+        <v>0.02988888704347655</v>
       </c>
       <c r="W58">
-        <v>0.2286263468714902</v>
+        <v>0.2287522004351482</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1267609048718872</v>
+        <v>0.124537029347819</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2091950734170073</v>
+        <v>0.2110950734170073</v>
       </c>
       <c r="C59">
-        <v>-6.354063964215328</v>
+        <v>-6.904587425291178</v>
       </c>
       <c r="D59">
-        <v>13.59103603578467</v>
+        <v>13.43481257470883</v>
       </c>
       <c r="E59">
-        <v>15.0451</v>
+        <v>15.4394</v>
       </c>
       <c r="F59">
-        <v>22.4751</v>
+        <v>22.8694</v>
       </c>
       <c r="G59">
         <v>2.53</v>
@@ -6113,37 +6113,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M59">
-        <v>5.29962858</v>
+        <v>5.392604520000001</v>
       </c>
       <c r="N59">
-        <v>-4.63962858</v>
+        <v>-4.732604520000001</v>
       </c>
       <c r="O59">
-        <v>-1.1135108592</v>
+        <v>-1.1358250848</v>
       </c>
       <c r="P59">
-        <v>-3.5261177208</v>
+        <v>-3.5967794352</v>
       </c>
       <c r="Q59">
-        <v>-1.5461177208</v>
+        <v>-1.6167794352</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1832705096952857</v>
+        <v>0.186543617068983</v>
       </c>
       <c r="T59">
-        <v>1.892333310540446</v>
+        <v>1.937388865553314</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02988888704347655</v>
+        <v>0.02937356140479591</v>
       </c>
       <c r="W59">
-        <v>0.2287522004351482</v>
+        <v>0.2288737142207491</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.124537029347819</v>
+        <v>0.1223898391866497</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2110950734170073</v>
+        <v>0.2129950734170073</v>
       </c>
       <c r="C60">
-        <v>-6.904587425291171</v>
+        <v>-7.451560248540458</v>
       </c>
       <c r="D60">
-        <v>13.43481257470883</v>
+        <v>13.28213975145954</v>
       </c>
       <c r="E60">
-        <v>15.4394</v>
+        <v>15.8337</v>
       </c>
       <c r="F60">
-        <v>22.8694</v>
+        <v>23.2637</v>
       </c>
       <c r="G60">
         <v>2.53</v>
@@ -6195,37 +6195,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M60">
-        <v>5.39260452</v>
+        <v>5.48558046</v>
       </c>
       <c r="N60">
-        <v>-4.73260452</v>
+        <v>-4.82558046</v>
       </c>
       <c r="O60">
-        <v>-1.1358250848</v>
+        <v>-1.1581393104</v>
       </c>
       <c r="P60">
-        <v>-3.5967794352</v>
+        <v>-3.6674411496</v>
       </c>
       <c r="Q60">
-        <v>-1.6167794352</v>
+        <v>-1.6874411496</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1865436170689829</v>
+        <v>0.1899763882170069</v>
       </c>
       <c r="T60">
-        <v>1.937388865553313</v>
+        <v>1.984642252518028</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02937356140479592</v>
+        <v>0.02887570443183328</v>
       </c>
       <c r="W60">
-        <v>0.2288737142207491</v>
+        <v>0.2289911088949737</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1223898391866497</v>
+        <v>0.1203154351326386</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2129950734170073</v>
+        <v>0.2148950734170073</v>
       </c>
       <c r="C61">
-        <v>-7.451560248540458</v>
+        <v>-7.995102121871314</v>
       </c>
       <c r="D61">
-        <v>13.28213975145954</v>
+        <v>13.13289787812868</v>
       </c>
       <c r="E61">
-        <v>15.8337</v>
+        <v>16.228</v>
       </c>
       <c r="F61">
-        <v>23.2637</v>
+        <v>23.658</v>
       </c>
       <c r="G61">
         <v>2.53</v>
@@ -6277,37 +6277,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M61">
-        <v>5.48558046</v>
+        <v>5.5785564</v>
       </c>
       <c r="N61">
-        <v>-4.82558046</v>
+        <v>-4.9185564</v>
       </c>
       <c r="O61">
-        <v>-1.1581393104</v>
+        <v>-1.180453536</v>
       </c>
       <c r="P61">
-        <v>-3.6674411496</v>
+        <v>-3.738102864</v>
       </c>
       <c r="Q61">
-        <v>-1.6874411496</v>
+        <v>-1.758102864</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1899763882170069</v>
+        <v>0.1935807979224321</v>
       </c>
       <c r="T61">
-        <v>1.984642252518028</v>
+        <v>2.034258308830979</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02887570443183328</v>
+        <v>0.02839444269130272</v>
       </c>
       <c r="W61">
-        <v>0.2289911088949737</v>
+        <v>0.2291045904133908</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1203154351326386</v>
+        <v>0.118310177880428</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2148950734170073</v>
+        <v>0.2167950734170073</v>
       </c>
       <c r="C62">
-        <v>-7.995102121871314</v>
+        <v>-8.535327413576024</v>
       </c>
       <c r="D62">
-        <v>13.13289787812868</v>
+        <v>12.98697258642398</v>
       </c>
       <c r="E62">
-        <v>16.228</v>
+        <v>16.6223</v>
       </c>
       <c r="F62">
-        <v>23.658</v>
+        <v>24.0523</v>
       </c>
       <c r="G62">
         <v>2.53</v>
@@ -6359,37 +6359,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M62">
-        <v>5.5785564</v>
+        <v>5.67153234</v>
       </c>
       <c r="N62">
-        <v>-4.9185564</v>
+        <v>-5.01153234</v>
       </c>
       <c r="O62">
-        <v>-1.180453536</v>
+        <v>-1.2027677616</v>
       </c>
       <c r="P62">
-        <v>-3.738102864</v>
+        <v>-3.8087645784</v>
       </c>
       <c r="Q62">
-        <v>-1.758102864</v>
+        <v>-1.8287645784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1935807979224321</v>
+        <v>0.1973700491512124</v>
       </c>
       <c r="T62">
-        <v>2.034258308830979</v>
+        <v>2.086418778288184</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02839444269130272</v>
+        <v>0.02792896002423219</v>
       </c>
       <c r="W62">
-        <v>0.2291045904133908</v>
+        <v>0.2292143512262861</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.118310177880428</v>
+        <v>0.1163706667676341</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2167950734170073</v>
+        <v>0.2186950734170073</v>
       </c>
       <c r="C63">
-        <v>-8.535327413576024</v>
+        <v>-9.072345464625931</v>
       </c>
       <c r="D63">
-        <v>12.98697258642398</v>
+        <v>12.84425453537407</v>
       </c>
       <c r="E63">
-        <v>16.6223</v>
+        <v>17.0166</v>
       </c>
       <c r="F63">
-        <v>24.0523</v>
+        <v>24.4466</v>
       </c>
       <c r="G63">
         <v>2.53</v>
@@ -6441,37 +6441,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M63">
-        <v>5.67153234</v>
+        <v>5.76450828</v>
       </c>
       <c r="N63">
-        <v>-5.01153234</v>
+        <v>-5.10450828</v>
       </c>
       <c r="O63">
-        <v>-1.2027677616</v>
+        <v>-1.2250819872</v>
       </c>
       <c r="P63">
-        <v>-3.8087645784</v>
+        <v>-3.8794262928</v>
       </c>
       <c r="Q63">
-        <v>-1.8287645784</v>
+        <v>-1.8994262928</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1973700491512124</v>
+        <v>0.2013587346551917</v>
       </c>
       <c r="T63">
-        <v>2.086418778288184</v>
+        <v>2.141324535611557</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02792896002423219</v>
+        <v>0.02747849292706715</v>
       </c>
       <c r="W63">
-        <v>0.2292143512262861</v>
+        <v>0.2293205713677976</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1163706667676341</v>
+        <v>0.1144937205294465</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2186950734170073</v>
+        <v>0.2205950734170073</v>
       </c>
       <c r="C64">
-        <v>-9.072345464625931</v>
+        <v>-9.606260861903124</v>
       </c>
       <c r="D64">
-        <v>12.84425453537407</v>
+        <v>12.70463913809688</v>
       </c>
       <c r="E64">
-        <v>17.0166</v>
+        <v>17.4109</v>
       </c>
       <c r="F64">
-        <v>24.4466</v>
+        <v>24.8409</v>
       </c>
       <c r="G64">
         <v>2.53</v>
@@ -6523,37 +6523,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M64">
-        <v>5.76450828</v>
+        <v>5.857484220000001</v>
       </c>
       <c r="N64">
-        <v>-5.10450828</v>
+        <v>-5.197484220000001</v>
       </c>
       <c r="O64">
-        <v>-1.2250819872</v>
+        <v>-1.2473962128</v>
       </c>
       <c r="P64">
-        <v>-3.8794262928</v>
+        <v>-3.950088007200001</v>
       </c>
       <c r="Q64">
-        <v>-1.8994262928</v>
+        <v>-1.970088007200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2013587346551917</v>
+        <v>0.2055630247810077</v>
       </c>
       <c r="T64">
-        <v>2.141324535611557</v>
+        <v>2.199198171709167</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02747849292706715</v>
+        <v>0.02704232637266926</v>
       </c>
       <c r="W64">
-        <v>0.2293205713677976</v>
+        <v>0.2294234194413246</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1144937205294465</v>
+        <v>0.1126763598861219</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2205950734170073</v>
+        <v>0.2224950734170074</v>
       </c>
       <c r="C65">
-        <v>-9.606260861903124</v>
+        <v>-10.13717369380373</v>
       </c>
       <c r="D65">
-        <v>12.70463913809688</v>
+        <v>12.56802630619627</v>
       </c>
       <c r="E65">
-        <v>17.4109</v>
+        <v>17.8052</v>
       </c>
       <c r="F65">
-        <v>24.8409</v>
+        <v>25.2352</v>
       </c>
       <c r="G65">
         <v>2.53</v>
@@ -6605,37 +6605,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M65">
-        <v>5.857484220000001</v>
+        <v>5.95046016</v>
       </c>
       <c r="N65">
-        <v>-5.197484220000001</v>
+        <v>-5.290460159999999</v>
       </c>
       <c r="O65">
-        <v>-1.2473962128</v>
+        <v>-1.2697104384</v>
       </c>
       <c r="P65">
-        <v>-3.950088007200001</v>
+        <v>-4.0207497216</v>
       </c>
       <c r="Q65">
-        <v>-1.970088007200001</v>
+        <v>-2.0407497216</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2055630247810077</v>
+        <v>0.2100008865804801</v>
       </c>
       <c r="T65">
-        <v>2.199198171709167</v>
+        <v>2.260287009812199</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02704232637266926</v>
+        <v>0.0266197900230963</v>
       </c>
       <c r="W65">
-        <v>0.2294234194413246</v>
+        <v>0.2295230535125539</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1126763598861219</v>
+        <v>0.1109157917629012</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2224950734170074</v>
+        <v>0.2243950734170073</v>
       </c>
       <c r="C66">
-        <v>-10.13717369380373</v>
+        <v>-10.66517978952574</v>
       </c>
       <c r="D66">
-        <v>12.56802630619627</v>
+        <v>12.43432021047426</v>
       </c>
       <c r="E66">
-        <v>17.8052</v>
+        <v>18.1995</v>
       </c>
       <c r="F66">
-        <v>25.2352</v>
+        <v>25.6295</v>
       </c>
       <c r="G66">
         <v>2.53</v>
@@ -6687,37 +6687,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M66">
-        <v>5.95046016</v>
+        <v>6.0434361</v>
       </c>
       <c r="N66">
-        <v>-5.290460159999999</v>
+        <v>-5.3834361</v>
       </c>
       <c r="O66">
-        <v>-1.2697104384</v>
+        <v>-1.292024664</v>
       </c>
       <c r="P66">
-        <v>-4.0207497216</v>
+        <v>-4.091411436</v>
       </c>
       <c r="Q66">
-        <v>-2.0407497216</v>
+        <v>-2.111411436</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2100008865804801</v>
+        <v>0.2146923404827796</v>
       </c>
       <c r="T66">
-        <v>2.260287009812199</v>
+        <v>2.324866638663977</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0266197900230963</v>
+        <v>0.02621025479197174</v>
       </c>
       <c r="W66">
-        <v>0.2295230535125539</v>
+        <v>0.2296196219200531</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1109157917629012</v>
+        <v>0.1092093949665489</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2243950734170073</v>
+        <v>0.2262950734170073</v>
       </c>
       <c r="C67">
-        <v>-10.66517978952574</v>
+        <v>-11.19037094324337</v>
       </c>
       <c r="D67">
-        <v>12.43432021047426</v>
+        <v>12.30342905675663</v>
       </c>
       <c r="E67">
-        <v>18.1995</v>
+        <v>18.5938</v>
       </c>
       <c r="F67">
-        <v>25.6295</v>
+        <v>26.0238</v>
       </c>
       <c r="G67">
         <v>2.53</v>
@@ -6769,37 +6769,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M67">
-        <v>6.0434361</v>
+        <v>6.136412040000001</v>
       </c>
       <c r="N67">
-        <v>-5.3834361</v>
+        <v>-5.47641204</v>
       </c>
       <c r="O67">
-        <v>-1.292024664</v>
+        <v>-1.3143388896</v>
       </c>
       <c r="P67">
-        <v>-4.091411436</v>
+        <v>-4.1620731504</v>
       </c>
       <c r="Q67">
-        <v>-2.111411436</v>
+        <v>-2.1820731504</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2146923404827796</v>
+        <v>0.2196597622616848</v>
       </c>
       <c r="T67">
-        <v>2.324866638663977</v>
+        <v>2.393245069212917</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02621025479197174</v>
+        <v>0.02581312971936611</v>
       </c>
       <c r="W67">
-        <v>0.2296196219200531</v>
+        <v>0.2297132640121735</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1092093949665489</v>
+        <v>0.1075547071640255</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2262950734170073</v>
+        <v>0.2281950734170073</v>
       </c>
       <c r="C68">
-        <v>-11.19037094324337</v>
+        <v>-11.7128351242703</v>
       </c>
       <c r="D68">
-        <v>12.30342905675663</v>
+        <v>12.1752648757297</v>
       </c>
       <c r="E68">
-        <v>18.5938</v>
+        <v>18.9881</v>
       </c>
       <c r="F68">
-        <v>26.0238</v>
+        <v>26.4181</v>
       </c>
       <c r="G68">
         <v>2.53</v>
@@ -6851,37 +6851,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M68">
-        <v>6.136412040000001</v>
+        <v>6.229387980000001</v>
       </c>
       <c r="N68">
-        <v>-5.47641204</v>
+        <v>-5.569387980000001</v>
       </c>
       <c r="O68">
-        <v>-1.3143388896</v>
+        <v>-1.3366531152</v>
       </c>
       <c r="P68">
-        <v>-4.1620731504</v>
+        <v>-4.232734864800001</v>
       </c>
       <c r="Q68">
-        <v>-2.1820731504</v>
+        <v>-2.252734864800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2196597622616848</v>
+        <v>0.2249282399059783</v>
       </c>
       <c r="T68">
-        <v>2.393245069212917</v>
+        <v>2.465767647067854</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02581312971936611</v>
+        <v>0.02542785912653974</v>
       </c>
       <c r="W68">
-        <v>0.2297132640121735</v>
+        <v>0.2298041108179619</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1075547071640255</v>
+        <v>0.1059494130272489</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2281950734170073</v>
+        <v>0.2300950734170074</v>
       </c>
       <c r="C69">
-        <v>-11.7128351242703</v>
+        <v>-12.23265667422266</v>
       </c>
       <c r="D69">
-        <v>12.1752648757297</v>
+        <v>12.04974332577734</v>
       </c>
       <c r="E69">
-        <v>18.9881</v>
+        <v>19.3824</v>
       </c>
       <c r="F69">
-        <v>26.4181</v>
+        <v>26.8124</v>
       </c>
       <c r="G69">
         <v>2.53</v>
@@ -6933,37 +6933,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M69">
-        <v>6.229387980000001</v>
+        <v>6.32236392</v>
       </c>
       <c r="N69">
-        <v>-5.569387980000001</v>
+        <v>-5.66236392</v>
       </c>
       <c r="O69">
-        <v>-1.3366531152</v>
+        <v>-1.3589673408</v>
       </c>
       <c r="P69">
-        <v>-4.232734864800001</v>
+        <v>-4.3033965792</v>
       </c>
       <c r="Q69">
-        <v>-2.252734864800001</v>
+        <v>-2.3233965792</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2249282399059783</v>
+        <v>0.2305259974030402</v>
       </c>
       <c r="T69">
-        <v>2.465767647067854</v>
+        <v>2.542822886038725</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02542785912653974</v>
+        <v>0.0250539200217377</v>
       </c>
       <c r="W69">
-        <v>0.2298041108179619</v>
+        <v>0.2298922856588743</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1059494130272489</v>
+        <v>0.1043913334239071</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2300950734170074</v>
+        <v>0.2319950734170074</v>
       </c>
       <c r="C70">
-        <v>-12.23265667422266</v>
+        <v>-12.74991649211055</v>
       </c>
       <c r="D70">
-        <v>12.04974332577734</v>
+        <v>11.92678350788945</v>
       </c>
       <c r="E70">
-        <v>19.3824</v>
+        <v>19.7767</v>
       </c>
       <c r="F70">
-        <v>26.8124</v>
+        <v>27.2067</v>
       </c>
       <c r="G70">
         <v>2.53</v>
@@ -7015,37 +7015,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M70">
-        <v>6.32236392</v>
+        <v>6.41533986</v>
       </c>
       <c r="N70">
-        <v>-5.66236392</v>
+        <v>-5.75533986</v>
       </c>
       <c r="O70">
-        <v>-1.3589673408</v>
+        <v>-1.3812815664</v>
       </c>
       <c r="P70">
-        <v>-4.3033965792</v>
+        <v>-4.3740582936</v>
       </c>
       <c r="Q70">
-        <v>-2.3233965792</v>
+        <v>-2.3940582936</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2305259974030402</v>
+        <v>0.2364849005450737</v>
       </c>
       <c r="T70">
-        <v>2.542822886038725</v>
+        <v>2.624849430749651</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0250539200217377</v>
+        <v>0.02469081973156758</v>
       </c>
       <c r="W70">
-        <v>0.2298922856588743</v>
+        <v>0.2299779047072964</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1043913334239071</v>
+        <v>0.1028784155481983</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2319950734170074</v>
+        <v>0.2338950734170074</v>
       </c>
       <c r="C71">
-        <v>-12.74991649211055</v>
+        <v>-13.26469220821158</v>
       </c>
       <c r="D71">
-        <v>11.92678350788945</v>
+        <v>11.80630779178842</v>
       </c>
       <c r="E71">
-        <v>19.7767</v>
+        <v>20.171</v>
       </c>
       <c r="F71">
-        <v>27.2067</v>
+        <v>27.601</v>
       </c>
       <c r="G71">
         <v>2.53</v>
@@ -7097,37 +7097,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M71">
-        <v>6.41533986</v>
+        <v>6.508315800000001</v>
       </c>
       <c r="N71">
-        <v>-5.75533986</v>
+        <v>-5.848315800000001</v>
       </c>
       <c r="O71">
-        <v>-1.3812815664</v>
+        <v>-1.403595792</v>
       </c>
       <c r="P71">
-        <v>-4.3740582936</v>
+        <v>-4.444720008000001</v>
       </c>
       <c r="Q71">
-        <v>-2.3940582936</v>
+        <v>-2.464720008000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2364849005450737</v>
+        <v>0.2428410638965762</v>
       </c>
       <c r="T71">
-        <v>2.624849430749651</v>
+        <v>2.71234441177464</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02469081973156758</v>
+        <v>0.02433809373540233</v>
       </c>
       <c r="W71">
-        <v>0.2299779047072964</v>
+        <v>0.2300610774971922</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1028784155481983</v>
+        <v>0.1014087238975098</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2338950734170074</v>
+        <v>0.2357950734170073</v>
       </c>
       <c r="C72">
-        <v>-13.26469220821158</v>
+        <v>-13.77705834751175</v>
       </c>
       <c r="D72">
-        <v>11.80630779178842</v>
+        <v>11.68824165248826</v>
       </c>
       <c r="E72">
-        <v>20.171</v>
+        <v>20.5653</v>
       </c>
       <c r="F72">
-        <v>27.601</v>
+        <v>27.9953</v>
       </c>
       <c r="G72">
         <v>2.53</v>
@@ -7179,37 +7179,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M72">
-        <v>6.508315800000001</v>
+        <v>6.601291740000002</v>
       </c>
       <c r="N72">
-        <v>-5.848315800000001</v>
+        <v>-5.941291740000001</v>
       </c>
       <c r="O72">
-        <v>-1.403595792</v>
+        <v>-1.4259100176</v>
       </c>
       <c r="P72">
-        <v>-4.444720008000001</v>
+        <v>-4.515381722400001</v>
       </c>
       <c r="Q72">
-        <v>-2.464720008000001</v>
+        <v>-2.535381722400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2428410638965762</v>
+        <v>0.2496355833412857</v>
       </c>
       <c r="T72">
-        <v>2.71234441177464</v>
+        <v>2.805873529422041</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02433809373540233</v>
+        <v>0.02399530368279103</v>
       </c>
       <c r="W72">
-        <v>0.2300610774971922</v>
+        <v>0.2301419073915979</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1014087238975098</v>
+        <v>0.09998043201162932</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2357950734170073</v>
+        <v>0.2376950734170074</v>
       </c>
       <c r="C73">
-        <v>-13.77705834751174</v>
+        <v>-14.28708648343668</v>
       </c>
       <c r="D73">
-        <v>11.68824165248826</v>
+        <v>11.57251351656332</v>
       </c>
       <c r="E73">
-        <v>20.5653</v>
+        <v>20.9596</v>
       </c>
       <c r="F73">
-        <v>27.9953</v>
+        <v>28.3896</v>
       </c>
       <c r="G73">
         <v>2.53</v>
@@ -7261,37 +7261,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M73">
-        <v>6.60129174</v>
+        <v>6.694267679999999</v>
       </c>
       <c r="N73">
-        <v>-5.94129174</v>
+        <v>-6.034267679999999</v>
       </c>
       <c r="O73">
-        <v>-1.4259100176</v>
+        <v>-1.4482242432</v>
       </c>
       <c r="P73">
-        <v>-4.5153817224</v>
+        <v>-4.586043436799999</v>
       </c>
       <c r="Q73">
-        <v>-2.5353817224</v>
+        <v>-2.606043436799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2496355833412857</v>
+        <v>0.2569154256034744</v>
       </c>
       <c r="T73">
-        <v>2.80587352942204</v>
+        <v>2.90608329832997</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02399530368279103</v>
+        <v>0.0236620355760856</v>
       </c>
       <c r="W73">
-        <v>0.2301419073915979</v>
+        <v>0.230220492011159</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.09998043201162932</v>
+        <v>0.09859181490035673</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2376950734170074</v>
+        <v>0.2395950734170073</v>
       </c>
       <c r="C74">
-        <v>-14.28708648343668</v>
+        <v>-14.79484538253963</v>
       </c>
       <c r="D74">
-        <v>11.57251351656332</v>
+        <v>11.45905461746037</v>
       </c>
       <c r="E74">
-        <v>20.9596</v>
+        <v>21.3539</v>
       </c>
       <c r="F74">
-        <v>28.3896</v>
+        <v>28.7839</v>
       </c>
       <c r="G74">
         <v>2.53</v>
@@ -7343,37 +7343,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M74">
-        <v>6.694267679999999</v>
+        <v>6.78724362</v>
       </c>
       <c r="N74">
-        <v>-6.034267679999999</v>
+        <v>-6.12724362</v>
       </c>
       <c r="O74">
-        <v>-1.4482242432</v>
+        <v>-1.4705384688</v>
       </c>
       <c r="P74">
-        <v>-4.586043436799999</v>
+        <v>-4.6567051512</v>
       </c>
       <c r="Q74">
-        <v>-2.606043436799999</v>
+        <v>-2.6767051512</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2569154256034744</v>
+        <v>0.2647345154406401</v>
       </c>
       <c r="T74">
-        <v>2.90608329832997</v>
+        <v>3.013716013082932</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0236620355760856</v>
+        <v>0.02333789810244059</v>
       </c>
       <c r="W74">
-        <v>0.230220492011159</v>
+        <v>0.2302969236274445</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09859181490035673</v>
+        <v>0.09724124209350249</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2395950734170073</v>
+        <v>0.2414950734170073</v>
       </c>
       <c r="C75">
-        <v>-14.79484538253963</v>
+        <v>-15.3004011407609</v>
       </c>
       <c r="D75">
-        <v>11.45905461746037</v>
+        <v>11.34779885923911</v>
       </c>
       <c r="E75">
-        <v>21.3539</v>
+        <v>21.7482</v>
       </c>
       <c r="F75">
-        <v>28.7839</v>
+        <v>29.1782</v>
       </c>
       <c r="G75">
         <v>2.53</v>
@@ -7425,37 +7425,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M75">
-        <v>6.78724362</v>
+        <v>6.88021956</v>
       </c>
       <c r="N75">
-        <v>-6.12724362</v>
+        <v>-6.22021956</v>
       </c>
       <c r="O75">
-        <v>-1.4705384688</v>
+        <v>-1.4928526944</v>
       </c>
       <c r="P75">
-        <v>-4.6567051512</v>
+        <v>-4.727366865600001</v>
       </c>
       <c r="Q75">
-        <v>-2.6767051512</v>
+        <v>-2.747366865600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2647345154406401</v>
+        <v>0.2731550737268186</v>
       </c>
       <c r="T75">
-        <v>3.013716013082932</v>
+        <v>3.129628167432275</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02333789810244059</v>
+        <v>0.02302252110105626</v>
       </c>
       <c r="W75">
-        <v>0.2302969236274445</v>
+        <v>0.2303712895243709</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09724124209350249</v>
+        <v>0.09592717125440109</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2414950734170073</v>
+        <v>0.2433950734170074</v>
       </c>
       <c r="C76">
-        <v>-15.3004011407609</v>
+        <v>-15.80381731182581</v>
       </c>
       <c r="D76">
-        <v>11.34779885923911</v>
+        <v>11.23868268817419</v>
       </c>
       <c r="E76">
-        <v>21.7482</v>
+        <v>22.1425</v>
       </c>
       <c r="F76">
-        <v>29.1782</v>
+        <v>29.5725</v>
       </c>
       <c r="G76">
         <v>2.53</v>
@@ -7507,37 +7507,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M76">
-        <v>6.88021956</v>
+        <v>6.9731955</v>
       </c>
       <c r="N76">
-        <v>-6.22021956</v>
+        <v>-6.3131955</v>
       </c>
       <c r="O76">
-        <v>-1.4928526944</v>
+        <v>-1.51516692</v>
       </c>
       <c r="P76">
-        <v>-4.727366865600001</v>
+        <v>-4.79802858</v>
       </c>
       <c r="Q76">
-        <v>-2.747366865600001</v>
+        <v>-2.81802858</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2731550737268186</v>
+        <v>0.2822492766758914</v>
       </c>
       <c r="T76">
-        <v>3.129628167432275</v>
+        <v>3.254813294129567</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02302252110105626</v>
+        <v>0.02271555415304218</v>
       </c>
       <c r="W76">
-        <v>0.2303712895243709</v>
+        <v>0.2304436723307127</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09592717125440109</v>
+        <v>0.09464814230434238</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2433950734170074</v>
+        <v>0.2452950734170073</v>
       </c>
       <c r="C77">
-        <v>-15.80381731182581</v>
+        <v>-16.30515502830563</v>
       </c>
       <c r="D77">
-        <v>11.23868268817419</v>
+        <v>11.13164497169437</v>
       </c>
       <c r="E77">
-        <v>22.1425</v>
+        <v>22.5368</v>
       </c>
       <c r="F77">
-        <v>29.5725</v>
+        <v>29.9668</v>
       </c>
       <c r="G77">
         <v>2.53</v>
@@ -7589,37 +7589,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M77">
-        <v>6.9731955</v>
+        <v>7.06617144</v>
       </c>
       <c r="N77">
-        <v>-6.3131955</v>
+        <v>-6.40617144</v>
       </c>
       <c r="O77">
-        <v>-1.51516692</v>
+        <v>-1.5374811456</v>
       </c>
       <c r="P77">
-        <v>-4.79802858</v>
+        <v>-4.868690294399999</v>
       </c>
       <c r="Q77">
-        <v>-2.81802858</v>
+        <v>-2.888690294399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2822492766758914</v>
+        <v>0.2921013298707202</v>
       </c>
       <c r="T77">
-        <v>3.254813294129567</v>
+        <v>3.390430514718299</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02271555415304218</v>
+        <v>0.02241666528260741</v>
       </c>
       <c r="W77">
-        <v>0.2304436723307127</v>
+        <v>0.2305141503263612</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09464814230434238</v>
+        <v>0.09340277201086422</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2452950734170073</v>
+        <v>0.2471950734170074</v>
       </c>
       <c r="C78">
-        <v>-16.30515502830563</v>
+        <v>-16.80447311582571</v>
       </c>
       <c r="D78">
-        <v>11.13164497169437</v>
+        <v>11.02662688417429</v>
       </c>
       <c r="E78">
-        <v>22.5368</v>
+        <v>22.9311</v>
       </c>
       <c r="F78">
-        <v>29.9668</v>
+        <v>30.3611</v>
       </c>
       <c r="G78">
         <v>2.53</v>
@@ -7671,37 +7671,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M78">
-        <v>7.06617144</v>
+        <v>7.15914738</v>
       </c>
       <c r="N78">
-        <v>-6.40617144</v>
+        <v>-6.49914738</v>
       </c>
       <c r="O78">
-        <v>-1.5374811456</v>
+        <v>-1.5597953712</v>
       </c>
       <c r="P78">
-        <v>-4.868690294399999</v>
+        <v>-4.9393520088</v>
       </c>
       <c r="Q78">
-        <v>-2.888690294399999</v>
+        <v>-2.9593520088</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2921013298707202</v>
+        <v>0.3028100833433602</v>
       </c>
       <c r="T78">
-        <v>3.390430514718299</v>
+        <v>3.537840537097355</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02241666528260741</v>
+        <v>0.02212553975945667</v>
       </c>
       <c r="W78">
-        <v>0.2305141503263612</v>
+        <v>0.2305827977247201</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09340277201086422</v>
+        <v>0.09218974899773613</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2471950734170074</v>
+        <v>0.2490950734170073</v>
       </c>
       <c r="C79">
-        <v>-16.80447311582571</v>
+        <v>-17.30182820086929</v>
       </c>
       <c r="D79">
-        <v>11.02662688417429</v>
+        <v>10.92357179913071</v>
       </c>
       <c r="E79">
-        <v>22.9311</v>
+        <v>23.3254</v>
       </c>
       <c r="F79">
-        <v>30.3611</v>
+        <v>30.7554</v>
       </c>
       <c r="G79">
         <v>2.53</v>
@@ -7753,37 +7753,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M79">
-        <v>7.15914738</v>
+        <v>7.252123320000001</v>
       </c>
       <c r="N79">
-        <v>-6.49914738</v>
+        <v>-6.592123320000001</v>
       </c>
       <c r="O79">
-        <v>-1.5597953712</v>
+        <v>-1.5821095968</v>
       </c>
       <c r="P79">
-        <v>-4.9393520088</v>
+        <v>-5.0100137232</v>
       </c>
       <c r="Q79">
-        <v>-2.9593520088</v>
+        <v>-3.0300137232</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3028100833433602</v>
+        <v>0.3144923598589675</v>
       </c>
       <c r="T79">
-        <v>3.537840537097355</v>
+        <v>3.698651470601781</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02212553975945667</v>
+        <v>0.02184187899330978</v>
       </c>
       <c r="W79">
-        <v>0.2305827977247201</v>
+        <v>0.2306496849333776</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09218974899773613</v>
+        <v>0.0910078291387908</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2490950734170073</v>
+        <v>0.2509950734170073</v>
       </c>
       <c r="C80">
-        <v>-17.30182820086929</v>
+        <v>-17.79727481259212</v>
       </c>
       <c r="D80">
-        <v>10.92357179913071</v>
+        <v>10.82242518740788</v>
       </c>
       <c r="E80">
-        <v>23.3254</v>
+        <v>23.7197</v>
       </c>
       <c r="F80">
-        <v>30.7554</v>
+        <v>31.1497</v>
       </c>
       <c r="G80">
         <v>2.53</v>
@@ -7835,37 +7835,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M80">
-        <v>7.252123320000001</v>
+        <v>7.345099260000001</v>
       </c>
       <c r="N80">
-        <v>-6.592123320000001</v>
+        <v>-6.685099260000001</v>
       </c>
       <c r="O80">
-        <v>-1.5821095968</v>
+        <v>-1.6044238224</v>
       </c>
       <c r="P80">
-        <v>-5.0100137232</v>
+        <v>-5.080675437600001</v>
       </c>
       <c r="Q80">
-        <v>-3.0300137232</v>
+        <v>-3.100675437600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3144923598589675</v>
+        <v>0.327287234137966</v>
       </c>
       <c r="T80">
-        <v>3.698651470601781</v>
+        <v>3.874777731106628</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02184187899330978</v>
+        <v>0.02156539951238181</v>
       </c>
       <c r="W80">
-        <v>0.2306496849333776</v>
+        <v>0.2307148787949804</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0910078291387908</v>
+        <v>0.08985583130159092</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2509950734170073</v>
+        <v>0.2528950734170073</v>
       </c>
       <c r="C81">
-        <v>-17.79727481259212</v>
+        <v>-18.29086547903241</v>
       </c>
       <c r="D81">
-        <v>10.82242518740788</v>
+        <v>10.72313452096759</v>
       </c>
       <c r="E81">
-        <v>23.7197</v>
+        <v>24.114</v>
       </c>
       <c r="F81">
-        <v>31.1497</v>
+        <v>31.544</v>
       </c>
       <c r="G81">
         <v>2.53</v>
@@ -7917,37 +7917,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M81">
-        <v>7.345099260000001</v>
+        <v>7.4380752</v>
       </c>
       <c r="N81">
-        <v>-6.685099260000001</v>
+        <v>-6.7780752</v>
       </c>
       <c r="O81">
-        <v>-1.6044238224</v>
+        <v>-1.626738048</v>
       </c>
       <c r="P81">
-        <v>-5.080675437600001</v>
+        <v>-5.151337152</v>
       </c>
       <c r="Q81">
-        <v>-3.100675437600001</v>
+        <v>-3.171337152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.327287234137966</v>
+        <v>0.3413615958448643</v>
       </c>
       <c r="T81">
-        <v>3.874777731106628</v>
+        <v>4.06851661766196</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02156539951238181</v>
+        <v>0.02129583201847704</v>
       </c>
       <c r="W81">
-        <v>0.2307148787949804</v>
+        <v>0.2307784428100431</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08985583130159092</v>
+        <v>0.088732633410321</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2528950734170073</v>
+        <v>0.2547950734170074</v>
       </c>
       <c r="C82">
-        <v>-18.29086547903241</v>
+        <v>-18.78265081807285</v>
       </c>
       <c r="D82">
-        <v>10.72313452096759</v>
+        <v>10.62564918192715</v>
       </c>
       <c r="E82">
-        <v>24.114</v>
+        <v>24.5083</v>
       </c>
       <c r="F82">
-        <v>31.544</v>
+        <v>31.9383</v>
       </c>
       <c r="G82">
         <v>2.53</v>
@@ -7999,37 +7999,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M82">
-        <v>7.4380752</v>
+        <v>7.531051140000001</v>
       </c>
       <c r="N82">
-        <v>-6.7780752</v>
+        <v>-6.871051140000001</v>
       </c>
       <c r="O82">
-        <v>-1.626738048</v>
+        <v>-1.6490522736</v>
       </c>
       <c r="P82">
-        <v>-5.151337152</v>
+        <v>-5.221998866400001</v>
       </c>
       <c r="Q82">
-        <v>-3.171337152</v>
+        <v>-3.241998866400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3413615958448643</v>
+        <v>0.3569174693103835</v>
       </c>
       <c r="T82">
-        <v>4.06851661766196</v>
+        <v>4.282649071223116</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02129583201847704</v>
+        <v>0.02103292051207609</v>
       </c>
       <c r="W82">
-        <v>0.2307784428100431</v>
+        <v>0.2308404373432525</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.088732633410321</v>
+        <v>0.08763716880031702</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2547950734170074</v>
+        <v>0.2566950734170074</v>
       </c>
       <c r="C83">
-        <v>-18.78265081807285</v>
+        <v>-19.27267962348568</v>
       </c>
       <c r="D83">
-        <v>10.62564918192715</v>
+        <v>10.52992037651432</v>
       </c>
       <c r="E83">
-        <v>24.5083</v>
+        <v>24.9026</v>
       </c>
       <c r="F83">
-        <v>31.9383</v>
+        <v>32.3326</v>
       </c>
       <c r="G83">
         <v>2.53</v>
@@ -8081,37 +8081,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M83">
-        <v>7.531051140000001</v>
+        <v>7.62402708</v>
       </c>
       <c r="N83">
-        <v>-6.871051140000001</v>
+        <v>-6.96402708</v>
       </c>
       <c r="O83">
-        <v>-1.6490522736</v>
+        <v>-1.6713664992</v>
       </c>
       <c r="P83">
-        <v>-5.221998866400001</v>
+        <v>-5.2926605808</v>
       </c>
       <c r="Q83">
-        <v>-3.241998866400001</v>
+        <v>-3.3126605808</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3569174693103835</v>
+        <v>0.3742017731609604</v>
       </c>
       <c r="T83">
-        <v>4.282649071223116</v>
+        <v>4.520574019624401</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02103292051207609</v>
+        <v>0.02077642148144102</v>
       </c>
       <c r="W83">
-        <v>0.2308404373432525</v>
+        <v>0.2309009198146762</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08763716880031702</v>
+        <v>0.08656842283933752</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2566950734170074</v>
+        <v>0.2585950734170073</v>
       </c>
       <c r="C84">
-        <v>-19.27267962348568</v>
+        <v>-19.76099894636808</v>
       </c>
       <c r="D84">
-        <v>10.52992037651432</v>
+        <v>10.43590105363192</v>
       </c>
       <c r="E84">
-        <v>24.9026</v>
+        <v>25.2969</v>
       </c>
       <c r="F84">
-        <v>32.3326</v>
+        <v>32.7269</v>
       </c>
       <c r="G84">
         <v>2.53</v>
@@ -8163,37 +8163,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M84">
-        <v>7.62402708</v>
+        <v>7.717003020000001</v>
       </c>
       <c r="N84">
-        <v>-6.96402708</v>
+        <v>-7.057003020000001</v>
       </c>
       <c r="O84">
-        <v>-1.6713664992</v>
+        <v>-1.6936807248</v>
       </c>
       <c r="P84">
-        <v>-5.2926605808</v>
+        <v>-5.363322295200001</v>
       </c>
       <c r="Q84">
-        <v>-3.3126605808</v>
+        <v>-3.383322295200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3742017731609604</v>
+        <v>0.3935195245233698</v>
       </c>
       <c r="T84">
-        <v>4.520574019624401</v>
+        <v>4.786490138425836</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02077642148144102</v>
+        <v>0.02052610315033932</v>
       </c>
       <c r="W84">
-        <v>0.2309009198146762</v>
+        <v>0.23095994487715</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08656842283933752</v>
+        <v>0.08552542979308053</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2585950734170073</v>
+        <v>0.2604950734170074</v>
       </c>
       <c r="C85">
-        <v>-19.76099894636808</v>
+        <v>-20.24765417225344</v>
       </c>
       <c r="D85">
-        <v>10.43590105363192</v>
+        <v>10.34354582774657</v>
       </c>
       <c r="E85">
-        <v>25.2969</v>
+        <v>25.6912</v>
       </c>
       <c r="F85">
-        <v>32.7269</v>
+        <v>33.1212</v>
       </c>
       <c r="G85">
         <v>2.53</v>
@@ -8245,37 +8245,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M85">
-        <v>7.717003020000001</v>
+        <v>7.80997896</v>
       </c>
       <c r="N85">
-        <v>-7.057003020000001</v>
+        <v>-7.14997896</v>
       </c>
       <c r="O85">
-        <v>-1.6936807248</v>
+        <v>-1.7159949504</v>
       </c>
       <c r="P85">
-        <v>-5.363322295200001</v>
+        <v>-5.4339840096</v>
       </c>
       <c r="Q85">
-        <v>-3.383322295200001</v>
+        <v>-3.453984009600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3935195245233698</v>
+        <v>0.4152519948060805</v>
       </c>
       <c r="T85">
-        <v>4.786490138425836</v>
+        <v>5.085645772077451</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02052610315033932</v>
+        <v>0.02028174477950195</v>
       </c>
       <c r="W85">
-        <v>0.23095994487715</v>
+        <v>0.2310175645809935</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08552542979308053</v>
+        <v>0.08450726991459145</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2604950734170073</v>
+        <v>0.2623950734170073</v>
       </c>
       <c r="C86">
-        <v>-20.24765417225344</v>
+        <v>-20.73268909416405</v>
       </c>
       <c r="D86">
-        <v>10.34354582774657</v>
+        <v>10.25281090583595</v>
       </c>
       <c r="E86">
-        <v>25.6912</v>
+        <v>26.0855</v>
       </c>
       <c r="F86">
-        <v>33.1212</v>
+        <v>33.5155</v>
       </c>
       <c r="G86">
         <v>2.53</v>
@@ -8327,37 +8327,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M86">
-        <v>7.80997896</v>
+        <v>7.902954899999999</v>
       </c>
       <c r="N86">
-        <v>-7.14997896</v>
+        <v>-7.242954899999999</v>
       </c>
       <c r="O86">
-        <v>-1.7159949504</v>
+        <v>-1.738309176</v>
       </c>
       <c r="P86">
-        <v>-5.4339840096</v>
+        <v>-5.504645724</v>
       </c>
       <c r="Q86">
-        <v>-3.453984009600001</v>
+        <v>-3.524645724</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4152519948060802</v>
+        <v>0.4398821277931522</v>
       </c>
       <c r="T86">
-        <v>5.085645772077448</v>
+        <v>5.424688823549277</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02028174477950195</v>
+        <v>0.02004313601739016</v>
       </c>
       <c r="W86">
-        <v>0.2310175645809935</v>
+        <v>0.2310738285270994</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08450726991459145</v>
+        <v>0.08351306673912562</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2623950734170073</v>
+        <v>0.2642950734170073</v>
       </c>
       <c r="C87">
-        <v>-20.73268909416405</v>
+        <v>-21.21614598185236</v>
       </c>
       <c r="D87">
-        <v>10.25281090583595</v>
+        <v>10.16365401814763</v>
       </c>
       <c r="E87">
-        <v>26.0855</v>
+        <v>26.4798</v>
       </c>
       <c r="F87">
-        <v>33.5155</v>
+        <v>33.9098</v>
       </c>
       <c r="G87">
         <v>2.53</v>
@@ -8409,37 +8409,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M87">
-        <v>7.902954899999999</v>
+        <v>7.99593084</v>
       </c>
       <c r="N87">
-        <v>-7.242954899999999</v>
+        <v>-7.33593084</v>
       </c>
       <c r="O87">
-        <v>-1.738309176</v>
+        <v>-1.7606234016</v>
       </c>
       <c r="P87">
-        <v>-5.504645724</v>
+        <v>-5.575307438399999</v>
       </c>
       <c r="Q87">
-        <v>-3.524645724</v>
+        <v>-3.595307438399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4398821277931522</v>
+        <v>0.4680308512069488</v>
       </c>
       <c r="T87">
-        <v>5.424688823549277</v>
+        <v>5.812166596659941</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02004313601739016</v>
+        <v>0.01981007629625772</v>
       </c>
       <c r="W87">
-        <v>0.2310738285270994</v>
+        <v>0.2311287840093424</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08351306673912562</v>
+        <v>0.08254198456774053</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2642950734170073</v>
+        <v>0.2661950734170073</v>
       </c>
       <c r="C88">
-        <v>-21.21614598185236</v>
+        <v>-21.69806564746051</v>
       </c>
       <c r="D88">
-        <v>10.16365401814763</v>
+        <v>10.07603435253949</v>
       </c>
       <c r="E88">
-        <v>26.4798</v>
+        <v>26.8741</v>
       </c>
       <c r="F88">
-        <v>33.9098</v>
+        <v>34.3041</v>
       </c>
       <c r="G88">
         <v>2.53</v>
@@ -8491,37 +8491,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M88">
-        <v>7.99593084</v>
+        <v>8.08890678</v>
       </c>
       <c r="N88">
-        <v>-7.33593084</v>
+        <v>-7.42890678</v>
       </c>
       <c r="O88">
-        <v>-1.7606234016</v>
+        <v>-1.7829376272</v>
       </c>
       <c r="P88">
-        <v>-5.575307438399999</v>
+        <v>-5.6459691528</v>
       </c>
       <c r="Q88">
-        <v>-3.595307438399999</v>
+        <v>-3.6659691528</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4680308512069488</v>
+        <v>0.5005101474536371</v>
       </c>
       <c r="T88">
-        <v>5.812166596659941</v>
+        <v>6.259256334864551</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01981007629625772</v>
+        <v>0.01958237426986395</v>
       </c>
       <c r="W88">
-        <v>0.2311287840093424</v>
+        <v>0.2311824761471661</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08254198456774053</v>
+        <v>0.08159322612443309</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2661950734170073</v>
+        <v>0.2680950734170073</v>
       </c>
       <c r="C89">
-        <v>-21.69806564746051</v>
+        <v>-22.17848750781281</v>
       </c>
       <c r="D89">
-        <v>10.07603435253949</v>
+        <v>9.989912492187186</v>
       </c>
       <c r="E89">
-        <v>26.8741</v>
+        <v>27.2684</v>
       </c>
       <c r="F89">
-        <v>34.3041</v>
+        <v>34.6984</v>
       </c>
       <c r="G89">
         <v>2.53</v>
@@ -8573,37 +8573,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M89">
-        <v>8.08890678</v>
+        <v>8.181882720000001</v>
       </c>
       <c r="N89">
-        <v>-7.42890678</v>
+        <v>-7.521882720000001</v>
       </c>
       <c r="O89">
-        <v>-1.7829376272</v>
+        <v>-1.8052518528</v>
       </c>
       <c r="P89">
-        <v>-5.6459691528</v>
+        <v>-5.716630867200001</v>
       </c>
       <c r="Q89">
-        <v>-3.6659691528</v>
+        <v>-3.736630867200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5005101474536371</v>
+        <v>0.5384026597414403</v>
       </c>
       <c r="T89">
-        <v>6.259256334864551</v>
+        <v>6.780861029436598</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01958237426986395</v>
+        <v>0.01935984728952458</v>
       </c>
       <c r="W89">
-        <v>0.2311824761471661</v>
+        <v>0.2312349480091301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08159322612443309</v>
+        <v>0.08066603037301912</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2680950734170073</v>
+        <v>0.2699950734170073</v>
       </c>
       <c r="C90">
-        <v>-22.17848750781281</v>
+        <v>-22.65744964354071</v>
       </c>
       <c r="D90">
-        <v>9.989912492187186</v>
+        <v>9.905250356459289</v>
       </c>
       <c r="E90">
-        <v>27.2684</v>
+        <v>27.6627</v>
       </c>
       <c r="F90">
-        <v>34.6984</v>
+        <v>35.0927</v>
       </c>
       <c r="G90">
         <v>2.53</v>
@@ -8655,37 +8655,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M90">
-        <v>8.181882720000001</v>
+        <v>8.274858660000001</v>
       </c>
       <c r="N90">
-        <v>-7.521882720000001</v>
+        <v>-7.614858660000001</v>
       </c>
       <c r="O90">
-        <v>-1.8052518528</v>
+        <v>-1.8275660784</v>
       </c>
       <c r="P90">
-        <v>-5.716630867200001</v>
+        <v>-5.787292581600001</v>
       </c>
       <c r="Q90">
-        <v>-3.736630867200001</v>
+        <v>-3.807292581600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5384026597414403</v>
+        <v>0.5831847197179348</v>
       </c>
       <c r="T90">
-        <v>6.780861029436598</v>
+        <v>7.397302941203561</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01935984728952458</v>
+        <v>0.01914232091548498</v>
       </c>
       <c r="W90">
-        <v>0.2312349480091301</v>
+        <v>0.2312862407281286</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08066603037301912</v>
+        <v>0.07975967048118737</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2699950734170073</v>
+        <v>0.2718950734170074</v>
       </c>
       <c r="C91">
-        <v>-22.65744964354071</v>
+        <v>-23.1349888552265</v>
       </c>
       <c r="D91">
-        <v>9.905250356459289</v>
+        <v>9.822011144773501</v>
       </c>
       <c r="E91">
-        <v>27.6627</v>
+        <v>28.057</v>
       </c>
       <c r="F91">
-        <v>35.0927</v>
+        <v>35.487</v>
       </c>
       <c r="G91">
         <v>2.53</v>
@@ -8737,37 +8737,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M91">
-        <v>8.274858660000001</v>
+        <v>8.3678346</v>
       </c>
       <c r="N91">
-        <v>-7.614858660000001</v>
+        <v>-7.7078346</v>
       </c>
       <c r="O91">
-        <v>-1.8275660784</v>
+        <v>-1.849880304</v>
       </c>
       <c r="P91">
-        <v>-5.787292581600001</v>
+        <v>-5.857954296</v>
       </c>
       <c r="Q91">
-        <v>-3.807292581600001</v>
+        <v>-3.877954296</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5831847197179348</v>
+        <v>0.6369231916897284</v>
       </c>
       <c r="T91">
-        <v>7.397302941203561</v>
+        <v>8.137033235323919</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01914232091548498</v>
+        <v>0.01892962846086848</v>
       </c>
       <c r="W91">
-        <v>0.2312862407281286</v>
+        <v>0.2313363936089272</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07975967048118737</v>
+        <v>0.07887345192028539</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2718950734170074</v>
+        <v>0.2737950734170074</v>
       </c>
       <c r="C92">
-        <v>-23.1349888552265</v>
+        <v>-23.61114071673992</v>
       </c>
       <c r="D92">
-        <v>9.822011144773501</v>
+        <v>9.740159283260086</v>
       </c>
       <c r="E92">
-        <v>28.057</v>
+        <v>28.4513</v>
       </c>
       <c r="F92">
-        <v>35.487</v>
+        <v>35.8813</v>
       </c>
       <c r="G92">
         <v>2.53</v>
@@ -8819,37 +8819,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M92">
-        <v>8.3678346</v>
+        <v>8.460810540000001</v>
       </c>
       <c r="N92">
-        <v>-7.7078346</v>
+        <v>-7.800810540000001</v>
       </c>
       <c r="O92">
-        <v>-1.849880304</v>
+        <v>-1.8721945296</v>
       </c>
       <c r="P92">
-        <v>-5.857954296</v>
+        <v>-5.928616010400001</v>
       </c>
       <c r="Q92">
-        <v>-3.877954296</v>
+        <v>-3.948616010400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6369231916897284</v>
+        <v>0.7026035463219206</v>
       </c>
       <c r="T92">
-        <v>8.137033235323919</v>
+        <v>9.0411480392488</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01892962846086848</v>
+        <v>0.0187216105656941</v>
       </c>
       <c r="W92">
-        <v>0.2313363936089272</v>
+        <v>0.2313854442286093</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07887345192028539</v>
+        <v>0.07800671069039211</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2737950734170074</v>
+        <v>0.2756950734170073</v>
       </c>
       <c r="C93">
-        <v>-23.61114071673992</v>
+        <v>-24.08593962592979</v>
       </c>
       <c r="D93">
-        <v>9.740159283260086</v>
+        <v>9.659660374070217</v>
       </c>
       <c r="E93">
-        <v>28.4513</v>
+        <v>28.8456</v>
       </c>
       <c r="F93">
-        <v>35.8813</v>
+        <v>36.2756</v>
       </c>
       <c r="G93">
         <v>2.53</v>
@@ -8901,37 +8901,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M93">
-        <v>8.460810540000001</v>
+        <v>8.553786480000001</v>
       </c>
       <c r="N93">
-        <v>-7.800810540000001</v>
+        <v>-7.893786480000001</v>
       </c>
       <c r="O93">
-        <v>-1.8721945296</v>
+        <v>-1.8945087552</v>
       </c>
       <c r="P93">
-        <v>-5.928616010400001</v>
+        <v>-5.999277724800001</v>
       </c>
       <c r="Q93">
-        <v>-3.948616010400001</v>
+        <v>-4.0192777248</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7026035463219206</v>
+        <v>0.7847039896121607</v>
       </c>
       <c r="T93">
-        <v>9.0411480392488</v>
+        <v>10.1712915441549</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0187216105656941</v>
+        <v>0.01851811479867569</v>
       </c>
       <c r="W93">
-        <v>0.2313854442286093</v>
+        <v>0.2314334285304723</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07800671069039211</v>
+        <v>0.07715881166114869</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2756950734170073</v>
+        <v>0.2775950734170073</v>
       </c>
       <c r="C94">
-        <v>-24.08593962592979</v>
+        <v>-24.55941885282265</v>
       </c>
       <c r="D94">
-        <v>9.659660374070217</v>
+        <v>9.580481147177352</v>
       </c>
       <c r="E94">
-        <v>28.8456</v>
+        <v>29.2399</v>
       </c>
       <c r="F94">
-        <v>36.2756</v>
+        <v>36.6699</v>
       </c>
       <c r="G94">
         <v>2.53</v>
@@ -8983,37 +8983,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M94">
-        <v>8.553786480000001</v>
+        <v>8.64676242</v>
       </c>
       <c r="N94">
-        <v>-7.893786480000001</v>
+        <v>-7.98676242</v>
       </c>
       <c r="O94">
-        <v>-1.8945087552</v>
+        <v>-1.9168229808</v>
       </c>
       <c r="P94">
-        <v>-5.999277724800001</v>
+        <v>-6.0699394392</v>
       </c>
       <c r="Q94">
-        <v>-4.0192777248</v>
+        <v>-4.0899394392</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7847039896121607</v>
+        <v>0.8902617024138982</v>
       </c>
       <c r="T94">
-        <v>10.1712915441549</v>
+        <v>11.62433319331989</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01851811479867569</v>
+        <v>0.01831899528471143</v>
       </c>
       <c r="W94">
-        <v>0.2314334285304723</v>
+        <v>0.231480380911865</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07715881166114869</v>
+        <v>0.07632914701963101</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2775950734170073</v>
+        <v>0.2794950734170074</v>
       </c>
       <c r="C95">
-        <v>-24.55941885282265</v>
+        <v>-25.03161058547015</v>
       </c>
       <c r="D95">
-        <v>9.580481147177352</v>
+        <v>9.502589414529846</v>
       </c>
       <c r="E95">
-        <v>29.2399</v>
+        <v>29.6342</v>
       </c>
       <c r="F95">
-        <v>36.6699</v>
+        <v>37.0642</v>
       </c>
       <c r="G95">
         <v>2.53</v>
@@ -9065,37 +9065,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M95">
-        <v>8.64676242</v>
+        <v>8.73973836</v>
       </c>
       <c r="N95">
-        <v>-7.98676242</v>
+        <v>-8.07973836</v>
       </c>
       <c r="O95">
-        <v>-1.9168229808</v>
+        <v>-1.9391372064</v>
       </c>
       <c r="P95">
-        <v>-6.0699394392</v>
+        <v>-6.1406011536</v>
       </c>
       <c r="Q95">
-        <v>-4.0899394392</v>
+        <v>-4.1606011536</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8902617024138982</v>
+        <v>1.031005319482882</v>
       </c>
       <c r="T95">
-        <v>11.62433319331989</v>
+        <v>13.56172205887321</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01831899528471143</v>
+        <v>0.01812411235615067</v>
       </c>
       <c r="W95">
-        <v>0.231480380911865</v>
+        <v>0.2315263343064197</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07632914701963101</v>
+        <v>0.0755171348172945</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2794950734170074</v>
+        <v>0.2813950734170074</v>
       </c>
       <c r="C96">
-        <v>-25.03161058547015</v>
+        <v>-25.50254597357799</v>
       </c>
       <c r="D96">
-        <v>9.502589414529846</v>
+        <v>9.425954026422009</v>
       </c>
       <c r="E96">
-        <v>29.6342</v>
+        <v>30.0285</v>
       </c>
       <c r="F96">
-        <v>37.0642</v>
+        <v>37.4585</v>
       </c>
       <c r="G96">
         <v>2.53</v>
@@ -9147,37 +9147,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M96">
-        <v>8.73973836</v>
+        <v>8.832714300000001</v>
       </c>
       <c r="N96">
-        <v>-8.07973836</v>
+        <v>-8.172714300000001</v>
       </c>
       <c r="O96">
-        <v>-1.9391372064</v>
+        <v>-1.961451432</v>
       </c>
       <c r="P96">
-        <v>-6.1406011536</v>
+        <v>-6.211262868</v>
       </c>
       <c r="Q96">
-        <v>-4.1606011536</v>
+        <v>-4.231262868</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.031005319482882</v>
+        <v>1.228046383379458</v>
       </c>
       <c r="T96">
-        <v>13.56172205887321</v>
+        <v>16.27406647064786</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01812411235615067</v>
+        <v>0.01793333222608593</v>
       </c>
       <c r="W96">
-        <v>0.2315263343064197</v>
+        <v>0.231571320261089</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0755171348172945</v>
+        <v>0.07472221760869135</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2813950734170074</v>
+        <v>0.2832950734170074</v>
       </c>
       <c r="C97">
-        <v>-25.50254597357799</v>
+        <v>-25.97225517004059</v>
       </c>
       <c r="D97">
-        <v>9.425954026422009</v>
+        <v>9.350544829959411</v>
       </c>
       <c r="E97">
-        <v>30.0285</v>
+        <v>30.4228</v>
       </c>
       <c r="F97">
-        <v>37.4585</v>
+        <v>37.8528</v>
       </c>
       <c r="G97">
         <v>2.53</v>
@@ -9229,37 +9229,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M97">
-        <v>8.832714300000001</v>
+        <v>8.925690240000002</v>
       </c>
       <c r="N97">
-        <v>-8.172714300000001</v>
+        <v>-8.265690240000001</v>
       </c>
       <c r="O97">
-        <v>-1.961451432</v>
+        <v>-1.9837656576</v>
       </c>
       <c r="P97">
-        <v>-6.211262868</v>
+        <v>-6.281924582400001</v>
       </c>
       <c r="Q97">
-        <v>-4.231262868</v>
+        <v>-4.301924582400002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.228046383379458</v>
+        <v>1.523607979224324</v>
       </c>
       <c r="T97">
-        <v>16.27406647064786</v>
+        <v>20.34258308830983</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01793333222608593</v>
+        <v>0.0177465266820642</v>
       </c>
       <c r="W97">
-        <v>0.231571320261089</v>
+        <v>0.2316153690083693</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07472221760869135</v>
+        <v>0.07394386117526752</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2832950734170073</v>
+        <v>0.2851950734170073</v>
       </c>
       <c r="C98">
-        <v>-25.97225517004058</v>
+        <v>-26.44076737049793</v>
       </c>
       <c r="D98">
-        <v>9.350544829959411</v>
+        <v>9.27633262950207</v>
       </c>
       <c r="E98">
-        <v>30.4228</v>
+        <v>30.8171</v>
       </c>
       <c r="F98">
-        <v>37.85279999999999</v>
+        <v>38.2471</v>
       </c>
       <c r="G98">
         <v>2.53</v>
@@ -9311,37 +9311,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M98">
-        <v>8.92569024</v>
+        <v>9.01866618</v>
       </c>
       <c r="N98">
-        <v>-8.26569024</v>
+        <v>-8.35866618</v>
       </c>
       <c r="O98">
-        <v>-1.9837656576</v>
+        <v>-2.0060798832</v>
       </c>
       <c r="P98">
-        <v>-6.2819245824</v>
+        <v>-6.3525862968</v>
       </c>
       <c r="Q98">
-        <v>-4.3019245824</v>
+        <v>-4.3725862968</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.52360797922432</v>
+        <v>2.01621063896576</v>
       </c>
       <c r="T98">
-        <v>20.34258308830978</v>
+        <v>27.12344411774637</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0177465266820642</v>
+        <v>0.01756357279874395</v>
       </c>
       <c r="W98">
-        <v>0.2316153690083693</v>
+        <v>0.2316585095340562</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07394386117526752</v>
+        <v>0.07318155332809984</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2851950734170073</v>
+        <v>0.2870950734170074</v>
       </c>
       <c r="C99">
-        <v>-26.44076737049793</v>
+        <v>-26.90811085102351</v>
       </c>
       <c r="D99">
-        <v>9.27633262950207</v>
+        <v>9.203289148976488</v>
       </c>
       <c r="E99">
-        <v>30.8171</v>
+        <v>31.2114</v>
       </c>
       <c r="F99">
-        <v>38.2471</v>
+        <v>38.6414</v>
       </c>
       <c r="G99">
         <v>2.53</v>
@@ -9393,37 +9393,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M99">
-        <v>9.01866618</v>
+        <v>9.111642119999999</v>
       </c>
       <c r="N99">
-        <v>-8.35866618</v>
+        <v>-8.451642119999999</v>
       </c>
       <c r="O99">
-        <v>-2.0060798832</v>
+        <v>-2.0283941088</v>
       </c>
       <c r="P99">
-        <v>-6.3525862968</v>
+        <v>-6.423248011199999</v>
       </c>
       <c r="Q99">
-        <v>-4.3725862968</v>
+        <v>-4.4432480112</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.01621063896576</v>
+        <v>3.001415958448639</v>
       </c>
       <c r="T99">
-        <v>27.12344411774637</v>
+        <v>40.68516617661955</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01756357279874395</v>
+        <v>0.01738435266814453</v>
       </c>
       <c r="W99">
-        <v>0.2316585095340562</v>
+        <v>0.2317007696408515</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07318155332809984</v>
+        <v>0.07243480278393555</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2870950734170074</v>
+        <v>0.2889950734170074</v>
       </c>
       <c r="C100">
-        <v>-26.90811085102351</v>
+        <v>-27.37431300404563</v>
       </c>
       <c r="D100">
-        <v>9.203289148976488</v>
+        <v>9.131386995954367</v>
       </c>
       <c r="E100">
-        <v>31.2114</v>
+        <v>31.6057</v>
       </c>
       <c r="F100">
-        <v>38.6414</v>
+        <v>39.0357</v>
       </c>
       <c r="G100">
         <v>2.53</v>
@@ -9475,37 +9475,37 @@
         <v>0.6600000000000001</v>
       </c>
       <c r="M100">
-        <v>9.111642119999999</v>
+        <v>9.20461806</v>
       </c>
       <c r="N100">
-        <v>-8.451642119999999</v>
+        <v>-8.544618059999999</v>
       </c>
       <c r="O100">
-        <v>-2.0283941088</v>
+        <v>-2.0507083344</v>
       </c>
       <c r="P100">
-        <v>-6.423248011199999</v>
+        <v>-6.4939097256</v>
       </c>
       <c r="Q100">
-        <v>-4.4432480112</v>
+        <v>-4.5139097256</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.001415958448639</v>
+        <v>5.957031916897279</v>
       </c>
       <c r="T100">
-        <v>40.68516617661955</v>
+        <v>81.37033235323911</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01738435266814453</v>
+        <v>0.01720875314624408</v>
       </c>
       <c r="W100">
-        <v>0.2317007696408515</v>
+        <v>0.2317421760081157</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07243480278393555</v>
+        <v>0.07170313810935036</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2889950734170074</v>
-      </c>
-      <c r="C101">
-        <v>-27.37431300404563</v>
-      </c>
-      <c r="D101">
-        <v>9.131386995954367</v>
-      </c>
-      <c r="E101">
-        <v>31.6057</v>
-      </c>
-      <c r="F101">
-        <v>39.0357</v>
-      </c>
-      <c r="G101">
-        <v>2.53</v>
-      </c>
-      <c r="H101">
-        <v>32</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.64</v>
-      </c>
-      <c r="K101">
-        <v>1.98</v>
-      </c>
-      <c r="L101">
-        <v>0.6600000000000001</v>
-      </c>
-      <c r="M101">
-        <v>9.20461806</v>
-      </c>
-      <c r="N101">
-        <v>-8.544618059999999</v>
-      </c>
-      <c r="O101">
-        <v>-2.0507083344</v>
-      </c>
-      <c r="P101">
-        <v>-6.4939097256</v>
-      </c>
-      <c r="Q101">
-        <v>-4.5139097256</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.957031916897279</v>
-      </c>
-      <c r="T101">
-        <v>81.37033235323911</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01720875314624408</v>
-      </c>
-      <c r="W101">
-        <v>0.2317421760081157</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07170313810935036</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
